--- a/14.xlsx
+++ b/14.xlsx
@@ -511,7 +511,7 @@
         <v>0.06684777140617371</v>
       </c>
       <c r="K2" t="n">
-        <v>2.987010000015289e-05</v>
+        <v>3.180499999871245e-05</v>
       </c>
     </row>
     <row r="3">
@@ -552,7 +552,7 @@
         <v>0.07220740616321564</v>
       </c>
       <c r="K3" t="n">
-        <v>5.179599999792117e-06</v>
+        <v>5.249900001217611e-06</v>
       </c>
     </row>
     <row r="4">
@@ -593,7 +593,7 @@
         <v>0.0724397674202919</v>
       </c>
       <c r="K4" t="n">
-        <v>4.920299999866984e-06</v>
+        <v>5.250400001386879e-06</v>
       </c>
     </row>
     <row r="5">
@@ -634,7 +634,7 @@
         <v>0.05048612505197525</v>
       </c>
       <c r="K5" t="n">
-        <v>5.011300000660413e-06</v>
+        <v>5.188700000871904e-06</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +675,7 @@
         <v>0.07279366999864578</v>
       </c>
       <c r="K6" t="n">
-        <v>4.890500000328757e-06</v>
+        <v>5.064499999207328e-06</v>
       </c>
     </row>
     <row r="7">
@@ -716,7 +716,7 @@
         <v>0.08528155833482742</v>
       </c>
       <c r="K7" t="n">
-        <v>5.4971999998088e-06</v>
+        <v>5.166499999177177e-06</v>
       </c>
     </row>
     <row r="8">
@@ -757,7 +757,7 @@
         <v>0.09551058709621429</v>
       </c>
       <c r="K8" t="n">
-        <v>5.119399999784946e-06</v>
+        <v>5.233700001554098e-06</v>
       </c>
     </row>
     <row r="9">
@@ -798,7 +798,7 @@
         <v>0.09153081476688385</v>
       </c>
       <c r="K9" t="n">
-        <v>4.85240000034537e-06</v>
+        <v>5.640800000037416e-06</v>
       </c>
     </row>
     <row r="10">
@@ -839,7 +839,7 @@
         <v>0.09214134514331818</v>
       </c>
       <c r="K10" t="n">
-        <v>4.440699999577191e-06</v>
+        <v>9.87130000066827e-06</v>
       </c>
     </row>
     <row r="11">
@@ -880,7 +880,7 @@
         <v>0.1158287227153778</v>
       </c>
       <c r="K11" t="n">
-        <v>6.277499999669089e-06</v>
+        <v>4.860099999859813e-06</v>
       </c>
     </row>
     <row r="12">
@@ -921,7 +921,7 @@
         <v>0.1135990023612976</v>
       </c>
       <c r="K12" t="n">
-        <v>6.082099999730417e-06</v>
+        <v>5.178200000955257e-06</v>
       </c>
     </row>
     <row r="13">
@@ -962,7 +962,7 @@
         <v>0.03732327371835709</v>
       </c>
       <c r="K13" t="n">
-        <v>5.33240000004298e-06</v>
+        <v>4.545000001598964e-06</v>
       </c>
     </row>
     <row r="14">
@@ -1003,7 +1003,7 @@
         <v>0.03716478496789932</v>
       </c>
       <c r="K14" t="n">
-        <v>4.519600000094215e-06</v>
+        <v>5.077899999378132e-06</v>
       </c>
     </row>
     <row r="15">
@@ -1044,7 +1044,7 @@
         <v>0.03989281505346298</v>
       </c>
       <c r="K15" t="n">
-        <v>5.274699999972654e-06</v>
+        <v>5.158899999514688e-06</v>
       </c>
     </row>
     <row r="16">
@@ -1085,7 +1085,7 @@
         <v>0.03747523203492165</v>
       </c>
       <c r="K16" t="n">
-        <v>4.737799999929848e-06</v>
+        <v>4.995900000722031e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1126,7 +1126,7 @@
         <v>0.05985265970230103</v>
       </c>
       <c r="K17" t="n">
-        <v>5.331000000296626e-06</v>
+        <v>6.154599999717903e-06</v>
       </c>
     </row>
     <row r="18">
@@ -1167,7 +1167,7 @@
         <v>0.06427808851003647</v>
       </c>
       <c r="K18" t="n">
-        <v>6.446399999731512e-06</v>
+        <v>6.956799999898066e-06</v>
       </c>
     </row>
     <row r="19">
@@ -1208,7 +1208,7 @@
         <v>0.06141677126288414</v>
       </c>
       <c r="K19" t="n">
-        <v>5.952100000286009e-06</v>
+        <v>7.135800000469317e-06</v>
       </c>
     </row>
     <row r="20">
@@ -1249,7 +1249,7 @@
         <v>0.05974716320633888</v>
       </c>
       <c r="K20" t="n">
-        <v>5.750199999965844e-06</v>
+        <v>5.842599999596132e-06</v>
       </c>
     </row>
     <row r="21">
@@ -1290,7 +1290,7 @@
         <v>0.06122929230332375</v>
       </c>
       <c r="K21" t="n">
-        <v>5.323200000020734e-06</v>
+        <v>5.507399999260088e-06</v>
       </c>
     </row>
     <row r="22">
@@ -1331,7 +1331,7 @@
         <v>0.0472424142062664</v>
       </c>
       <c r="K22" t="n">
-        <v>5.82269999995333e-06</v>
+        <v>5.214999999225256e-06</v>
       </c>
     </row>
     <row r="23">
@@ -1372,7 +1372,7 @@
         <v>0.04826546832919121</v>
       </c>
       <c r="K23" t="n">
-        <v>5.94849999924918e-06</v>
+        <v>6.724599999870406e-06</v>
       </c>
     </row>
     <row r="24">
@@ -1413,7 +1413,7 @@
         <v>0.050253976136446</v>
       </c>
       <c r="K24" t="n">
-        <v>5.293399999573012e-06</v>
+        <v>5.962499999441207e-06</v>
       </c>
     </row>
     <row r="25">
@@ -1454,7 +1454,7 @@
         <v>0.04755860194563866</v>
       </c>
       <c r="K25" t="n">
-        <v>5.892899999707879e-06</v>
+        <v>6.854999999632127e-06</v>
       </c>
     </row>
     <row r="26">
@@ -1495,7 +1495,7 @@
         <v>0.04773597046732903</v>
       </c>
       <c r="K26" t="n">
-        <v>5.71490000038466e-06</v>
+        <v>6.40939999902912e-06</v>
       </c>
     </row>
   </sheetData>

--- a/14.xlsx
+++ b/14.xlsx
@@ -511,7 +511,7 @@
         <v>0.06684777140617371</v>
       </c>
       <c r="K2" t="n">
-        <v>3.180499999871245e-05</v>
+        <v>4.029540000010457e-05</v>
       </c>
     </row>
     <row r="3">
@@ -552,7 +552,7 @@
         <v>0.07220740616321564</v>
       </c>
       <c r="K3" t="n">
-        <v>5.249900001217611e-06</v>
+        <v>5.434700000023441e-06</v>
       </c>
     </row>
     <row r="4">
@@ -593,7 +593,7 @@
         <v>0.0724397674202919</v>
       </c>
       <c r="K4" t="n">
-        <v>5.250400001386879e-06</v>
+        <v>5.927600000177335e-06</v>
       </c>
     </row>
     <row r="5">
@@ -634,7 +634,7 @@
         <v>0.05048612505197525</v>
       </c>
       <c r="K5" t="n">
-        <v>5.188700000871904e-06</v>
+        <v>5.781200000001263e-06</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +675,7 @@
         <v>0.07279366999864578</v>
       </c>
       <c r="K6" t="n">
-        <v>5.064499999207328e-06</v>
+        <v>5.939800000305695e-06</v>
       </c>
     </row>
     <row r="7">
@@ -716,7 +716,7 @@
         <v>0.08528155833482742</v>
       </c>
       <c r="K7" t="n">
-        <v>5.166499999177177e-06</v>
+        <v>6.461400000262074e-06</v>
       </c>
     </row>
     <row r="8">
@@ -757,7 +757,7 @@
         <v>0.09551058709621429</v>
       </c>
       <c r="K8" t="n">
-        <v>5.233700001554098e-06</v>
+        <v>6.865700000162178e-06</v>
       </c>
     </row>
     <row r="9">
@@ -798,7 +798,7 @@
         <v>0.09153081476688385</v>
       </c>
       <c r="K9" t="n">
-        <v>5.640800000037416e-06</v>
+        <v>5.78250000035041e-06</v>
       </c>
     </row>
     <row r="10">
@@ -839,7 +839,7 @@
         <v>0.09214134514331818</v>
       </c>
       <c r="K10" t="n">
-        <v>9.87130000066827e-06</v>
+        <v>5.745399999796063e-06</v>
       </c>
     </row>
     <row r="11">
@@ -880,7 +880,7 @@
         <v>0.1158287227153778</v>
       </c>
       <c r="K11" t="n">
-        <v>4.860099999859813e-06</v>
+        <v>6.495200000244949e-06</v>
       </c>
     </row>
     <row r="12">
@@ -921,7 +921,7 @@
         <v>0.1135990023612976</v>
       </c>
       <c r="K12" t="n">
-        <v>5.178200000955257e-06</v>
+        <v>5.921500000113156e-06</v>
       </c>
     </row>
     <row r="13">
@@ -962,7 +962,7 @@
         <v>0.03732327371835709</v>
       </c>
       <c r="K13" t="n">
-        <v>4.545000001598964e-06</v>
+        <v>6.450400000176159e-06</v>
       </c>
     </row>
     <row r="14">
@@ -1003,7 +1003,7 @@
         <v>0.03716478496789932</v>
       </c>
       <c r="K14" t="n">
-        <v>5.077899999378132e-06</v>
+        <v>6.502199999886216e-06</v>
       </c>
     </row>
     <row r="15">
@@ -1044,7 +1044,7 @@
         <v>0.03989281505346298</v>
       </c>
       <c r="K15" t="n">
-        <v>5.158899999514688e-06</v>
+        <v>5.932099999881757e-06</v>
       </c>
     </row>
     <row r="16">
@@ -1085,7 +1085,7 @@
         <v>0.03747523203492165</v>
       </c>
       <c r="K16" t="n">
-        <v>4.995900000722031e-06</v>
+        <v>5.909900000006019e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1126,7 +1126,7 @@
         <v>0.05985265970230103</v>
       </c>
       <c r="K17" t="n">
-        <v>6.154599999717903e-06</v>
+        <v>6.901299999753974e-06</v>
       </c>
     </row>
     <row r="18">
@@ -1167,7 +1167,7 @@
         <v>0.06427808851003647</v>
       </c>
       <c r="K18" t="n">
-        <v>6.956799999898066e-06</v>
+        <v>5.988700000216341e-06</v>
       </c>
     </row>
     <row r="19">
@@ -1208,7 +1208,7 @@
         <v>0.06141677126288414</v>
       </c>
       <c r="K19" t="n">
-        <v>7.135800000469317e-06</v>
+        <v>8.604699999978039e-06</v>
       </c>
     </row>
     <row r="20">
@@ -1249,7 +1249,7 @@
         <v>0.05974716320633888</v>
       </c>
       <c r="K20" t="n">
-        <v>5.842599999596132e-06</v>
+        <v>6.814100000156032e-06</v>
       </c>
     </row>
     <row r="21">
@@ -1290,7 +1290,7 @@
         <v>0.06122929230332375</v>
       </c>
       <c r="K21" t="n">
-        <v>5.507399999260088e-06</v>
+        <v>8.461299999908078e-06</v>
       </c>
     </row>
     <row r="22">
@@ -1331,7 +1331,7 @@
         <v>0.0472424142062664</v>
       </c>
       <c r="K22" t="n">
-        <v>5.214999999225256e-06</v>
+        <v>6.620599999678234e-06</v>
       </c>
     </row>
     <row r="23">
@@ -1372,7 +1372,7 @@
         <v>0.04826546832919121</v>
       </c>
       <c r="K23" t="n">
-        <v>6.724599999870406e-06</v>
+        <v>6.179599999995844e-06</v>
       </c>
     </row>
     <row r="24">
@@ -1413,7 +1413,7 @@
         <v>0.050253976136446</v>
       </c>
       <c r="K24" t="n">
-        <v>5.962499999441207e-06</v>
+        <v>6.872100000236969e-06</v>
       </c>
     </row>
     <row r="25">
@@ -1454,7 +1454,7 @@
         <v>0.04755860194563866</v>
       </c>
       <c r="K25" t="n">
-        <v>6.854999999632127e-06</v>
+        <v>6.665299999895069e-06</v>
       </c>
     </row>
     <row r="26">
@@ -1495,7 +1495,7 @@
         <v>0.04773597046732903</v>
       </c>
       <c r="K26" t="n">
-        <v>6.40939999902912e-06</v>
+        <v>6.746999999904801e-06</v>
       </c>
     </row>
   </sheetData>

--- a/14.xlsx
+++ b/14.xlsx
@@ -511,7 +511,7 @@
         <v>0.06684777140617371</v>
       </c>
       <c r="K2" t="n">
-        <v>4.029540000010457e-05</v>
+        <v>3.086480000092706e-05</v>
       </c>
     </row>
     <row r="3">
@@ -552,7 +552,7 @@
         <v>0.07220740616321564</v>
       </c>
       <c r="K3" t="n">
-        <v>5.434700000023441e-06</v>
+        <v>5.856099998709397e-06</v>
       </c>
     </row>
     <row r="4">
@@ -593,7 +593,7 @@
         <v>0.0724397674202919</v>
       </c>
       <c r="K4" t="n">
-        <v>5.927600000177335e-06</v>
+        <v>6.618800000069314e-06</v>
       </c>
     </row>
     <row r="5">
@@ -634,7 +634,7 @@
         <v>0.05048612505197525</v>
       </c>
       <c r="K5" t="n">
-        <v>5.781200000001263e-06</v>
+        <v>5.468299999847659e-06</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +675,7 @@
         <v>0.07279366999864578</v>
       </c>
       <c r="K6" t="n">
-        <v>5.939800000305695e-06</v>
+        <v>5.580699998972705e-06</v>
       </c>
     </row>
     <row r="7">
@@ -716,7 +716,7 @@
         <v>0.08528155833482742</v>
       </c>
       <c r="K7" t="n">
-        <v>6.461400000262074e-06</v>
+        <v>5.393999999796506e-06</v>
       </c>
     </row>
     <row r="8">
@@ -757,7 +757,7 @@
         <v>0.09551058709621429</v>
       </c>
       <c r="K8" t="n">
-        <v>6.865700000162178e-06</v>
+        <v>5.744899999626795e-06</v>
       </c>
     </row>
     <row r="9">
@@ -798,7 +798,7 @@
         <v>0.09153081476688385</v>
       </c>
       <c r="K9" t="n">
-        <v>5.78250000035041e-06</v>
+        <v>5.203499998970073e-06</v>
       </c>
     </row>
     <row r="10">
@@ -839,7 +839,7 @@
         <v>0.09214134514331818</v>
       </c>
       <c r="K10" t="n">
-        <v>5.745399999796063e-06</v>
+        <v>5.858000000444008e-06</v>
       </c>
     </row>
     <row r="11">
@@ -880,7 +880,7 @@
         <v>0.1158287227153778</v>
       </c>
       <c r="K11" t="n">
-        <v>6.495200000244949e-06</v>
+        <v>6.341000000247732e-06</v>
       </c>
     </row>
     <row r="12">
@@ -921,7 +921,7 @@
         <v>0.1135990023612976</v>
       </c>
       <c r="K12" t="n">
-        <v>5.921500000113156e-06</v>
+        <v>5.320799999026349e-06</v>
       </c>
     </row>
     <row r="13">
@@ -962,7 +962,7 @@
         <v>0.03732327371835709</v>
       </c>
       <c r="K13" t="n">
-        <v>6.450400000176159e-06</v>
+        <v>5.899200001294958e-06</v>
       </c>
     </row>
     <row r="14">
@@ -1003,7 +1003,7 @@
         <v>0.03716478496789932</v>
       </c>
       <c r="K14" t="n">
-        <v>6.502199999886216e-06</v>
+        <v>5.579699998634169e-06</v>
       </c>
     </row>
     <row r="15">
@@ -1044,7 +1044,7 @@
         <v>0.03989281505346298</v>
       </c>
       <c r="K15" t="n">
-        <v>5.932099999881757e-06</v>
+        <v>5.839199999172706e-06</v>
       </c>
     </row>
     <row r="16">
@@ -1085,7 +1085,7 @@
         <v>0.03747523203492165</v>
       </c>
       <c r="K16" t="n">
-        <v>5.909900000006019e-06</v>
+        <v>5.740100001276005e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1126,7 +1126,7 @@
         <v>0.05985265970230103</v>
       </c>
       <c r="K17" t="n">
-        <v>6.901299999753974e-06</v>
+        <v>6.008399999700487e-06</v>
       </c>
     </row>
     <row r="18">
@@ -1167,7 +1167,7 @@
         <v>0.06427808851003647</v>
       </c>
       <c r="K18" t="n">
-        <v>5.988700000216341e-06</v>
+        <v>6.503900000097929e-06</v>
       </c>
     </row>
     <row r="19">
@@ -1208,7 +1208,7 @@
         <v>0.06141677126288414</v>
       </c>
       <c r="K19" t="n">
-        <v>8.604699999978039e-06</v>
+        <v>6.577199999810545e-06</v>
       </c>
     </row>
     <row r="20">
@@ -1249,7 +1249,7 @@
         <v>0.05974716320633888</v>
       </c>
       <c r="K20" t="n">
-        <v>6.814100000156032e-06</v>
+        <v>6.451699999161064e-06</v>
       </c>
     </row>
     <row r="21">
@@ -1290,7 +1290,7 @@
         <v>0.06122929230332375</v>
       </c>
       <c r="K21" t="n">
-        <v>8.461299999908078e-06</v>
+        <v>6.573199998456403e-06</v>
       </c>
     </row>
     <row r="22">
@@ -1331,7 +1331,7 @@
         <v>0.0472424142062664</v>
       </c>
       <c r="K22" t="n">
-        <v>6.620599999678234e-06</v>
+        <v>6.541300001117633e-06</v>
       </c>
     </row>
     <row r="23">
@@ -1372,7 +1372,7 @@
         <v>0.04826546832919121</v>
       </c>
       <c r="K23" t="n">
-        <v>6.179599999995844e-06</v>
+        <v>6.587599998965743e-06</v>
       </c>
     </row>
     <row r="24">
@@ -1413,7 +1413,7 @@
         <v>0.050253976136446</v>
       </c>
       <c r="K24" t="n">
-        <v>6.872100000236969e-06</v>
+        <v>6.46989999950165e-06</v>
       </c>
     </row>
     <row r="25">
@@ -1454,7 +1454,7 @@
         <v>0.04755860194563866</v>
       </c>
       <c r="K25" t="n">
-        <v>6.665299999895069e-06</v>
+        <v>6.466400000135764e-06</v>
       </c>
     </row>
     <row r="26">
@@ -1495,7 +1495,7 @@
         <v>0.04773597046732903</v>
       </c>
       <c r="K26" t="n">
-        <v>6.746999999904801e-06</v>
+        <v>6.556000000273343e-06</v>
       </c>
     </row>
   </sheetData>

--- a/14.xlsx
+++ b/14.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
         <v>0.06684777140617371</v>
       </c>
       <c r="K2" t="n">
-        <v>3.086480000092706e-05</v>
+        <v>1.092070000595413e-05</v>
       </c>
     </row>
     <row r="3">
@@ -552,7 +552,7 @@
         <v>0.07220740616321564</v>
       </c>
       <c r="K3" t="n">
-        <v>5.856099998709397e-06</v>
+        <v>5.82649999705609e-06</v>
       </c>
     </row>
     <row r="4">
@@ -593,7 +593,7 @@
         <v>0.0724397674202919</v>
       </c>
       <c r="K4" t="n">
-        <v>6.618800000069314e-06</v>
+        <v>8.519299997715279e-06</v>
       </c>
     </row>
     <row r="5">
@@ -634,7 +634,7 @@
         <v>0.05048612505197525</v>
       </c>
       <c r="K5" t="n">
-        <v>5.468299999847659e-06</v>
+        <v>5.750500000431203e-06</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +675,7 @@
         <v>0.07279366999864578</v>
       </c>
       <c r="K6" t="n">
-        <v>5.580699998972705e-06</v>
+        <v>6.05379999615252e-06</v>
       </c>
     </row>
     <row r="7">
@@ -716,7 +716,7 @@
         <v>0.08528155833482742</v>
       </c>
       <c r="K7" t="n">
-        <v>5.393999999796506e-06</v>
+        <v>7.896299997810275e-06</v>
       </c>
     </row>
     <row r="8">
@@ -757,7 +757,7 @@
         <v>0.09551058709621429</v>
       </c>
       <c r="K8" t="n">
-        <v>5.744899999626795e-06</v>
+        <v>5.546200001845136e-06</v>
       </c>
     </row>
     <row r="9">
@@ -798,7 +798,7 @@
         <v>0.09153081476688385</v>
       </c>
       <c r="K9" t="n">
-        <v>5.203499998970073e-06</v>
+        <v>5.622199998470023e-06</v>
       </c>
     </row>
     <row r="10">
@@ -839,7 +839,7 @@
         <v>0.09214134514331818</v>
       </c>
       <c r="K10" t="n">
-        <v>5.858000000444008e-06</v>
+        <v>5.189500006963499e-06</v>
       </c>
     </row>
     <row r="11">
@@ -880,7 +880,7 @@
         <v>0.1158287227153778</v>
       </c>
       <c r="K11" t="n">
-        <v>6.341000000247732e-06</v>
+        <v>5.625499994494021e-06</v>
       </c>
     </row>
     <row r="12">
@@ -921,7 +921,7 @@
         <v>0.1135990023612976</v>
       </c>
       <c r="K12" t="n">
-        <v>5.320799999026349e-06</v>
+        <v>5.79979999747593e-06</v>
       </c>
     </row>
     <row r="13">
@@ -962,7 +962,7 @@
         <v>0.03732327371835709</v>
       </c>
       <c r="K13" t="n">
-        <v>5.899200001294958e-06</v>
+        <v>5.113099992740899e-06</v>
       </c>
     </row>
     <row r="14">
@@ -1003,7 +1003,7 @@
         <v>0.03716478496789932</v>
       </c>
       <c r="K14" t="n">
-        <v>5.579699998634169e-06</v>
+        <v>5.368300000554882e-06</v>
       </c>
     </row>
     <row r="15">
@@ -1044,7 +1044,7 @@
         <v>0.03989281505346298</v>
       </c>
       <c r="K15" t="n">
-        <v>5.839199999172706e-06</v>
+        <v>6.724100006977096e-06</v>
       </c>
     </row>
     <row r="16">
@@ -1085,7 +1085,7 @@
         <v>0.03747523203492165</v>
       </c>
       <c r="K16" t="n">
-        <v>5.740100001276005e-06</v>
+        <v>5.641099996864796e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1126,7 +1126,7 @@
         <v>0.05985265970230103</v>
       </c>
       <c r="K17" t="n">
-        <v>6.008399999700487e-06</v>
+        <v>6.653599994024261e-06</v>
       </c>
     </row>
     <row r="18">
@@ -1167,7 +1167,7 @@
         <v>0.06427808851003647</v>
       </c>
       <c r="K18" t="n">
-        <v>6.503900000097929e-06</v>
+        <v>6.860399997094646e-06</v>
       </c>
     </row>
     <row r="19">
@@ -1208,7 +1208,7 @@
         <v>0.06141677126288414</v>
       </c>
       <c r="K19" t="n">
-        <v>6.577199999810545e-06</v>
+        <v>6.0174999962328e-06</v>
       </c>
     </row>
     <row r="20">
@@ -1249,7 +1249,7 @@
         <v>0.05974716320633888</v>
       </c>
       <c r="K20" t="n">
-        <v>6.451699999161064e-06</v>
+        <v>6.070099989301525e-06</v>
       </c>
     </row>
     <row r="21">
@@ -1290,7 +1290,7 @@
         <v>0.06122929230332375</v>
       </c>
       <c r="K21" t="n">
-        <v>6.573199998456403e-06</v>
+        <v>5.940399991231971e-06</v>
       </c>
     </row>
     <row r="22">
@@ -1331,7 +1331,7 @@
         <v>0.0472424142062664</v>
       </c>
       <c r="K22" t="n">
-        <v>6.541300001117633e-06</v>
+        <v>5.804500004160218e-06</v>
       </c>
     </row>
     <row r="23">
@@ -1372,7 +1372,7 @@
         <v>0.04826546832919121</v>
       </c>
       <c r="K23" t="n">
-        <v>6.587599998965743e-06</v>
+        <v>5.851299996720627e-06</v>
       </c>
     </row>
     <row r="24">
@@ -1413,7 +1413,7 @@
         <v>0.050253976136446</v>
       </c>
       <c r="K24" t="n">
-        <v>6.46989999950165e-06</v>
+        <v>6.453699999838136e-06</v>
       </c>
     </row>
     <row r="25">
@@ -1454,7 +1454,7 @@
         <v>0.04755860194563866</v>
       </c>
       <c r="K25" t="n">
-        <v>6.466400000135764e-06</v>
+        <v>6.597199986572377e-06</v>
       </c>
     </row>
     <row r="26">
@@ -1495,7 +1495,89 @@
         <v>0.04773597046732903</v>
       </c>
       <c r="K26" t="n">
-        <v>6.556000000273343e-06</v>
+        <v>6.632499993429519e-06</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ablated PINN</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Run 1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>-862.21 (18.28)</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.04733014106750488</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.007503214292228222</v>
+      </c>
+      <c r="F27" t="n">
+        <v>8.668375968933105</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.2386341094970703</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.028512477874756</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.613296508789062</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.020527601242065</v>
+      </c>
+      <c r="K27" t="n">
+        <v>7.106500008376315e-06</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ablated PINN</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Run 2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>-279.66 (4.74)</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.0707341730594635</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.01563688926398754</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.134171009063721</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.1762083172798157</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.8491321206092834</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.559596538543701</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.213654160499573</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.980800003977492e-06</v>
       </c>
     </row>
   </sheetData>

--- a/14.xlsx
+++ b/14.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
         <v>0.06684777140617371</v>
       </c>
       <c r="K2" t="n">
-        <v>1.092070000595413e-05</v>
+        <v>3.231809999851976e-05</v>
       </c>
     </row>
     <row r="3">
@@ -552,7 +552,7 @@
         <v>0.07220740616321564</v>
       </c>
       <c r="K3" t="n">
-        <v>5.82649999705609e-06</v>
+        <v>5.294900009175762e-06</v>
       </c>
     </row>
     <row r="4">
@@ -593,7 +593,7 @@
         <v>0.0724397674202919</v>
       </c>
       <c r="K4" t="n">
-        <v>8.519299997715279e-06</v>
+        <v>5.51820000691805e-06</v>
       </c>
     </row>
     <row r="5">
@@ -634,7 +634,7 @@
         <v>0.05048612505197525</v>
       </c>
       <c r="K5" t="n">
-        <v>5.750500000431203e-06</v>
+        <v>7.407400000374764e-06</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +675,7 @@
         <v>0.07279366999864578</v>
       </c>
       <c r="K6" t="n">
-        <v>6.05379999615252e-06</v>
+        <v>5.736499995691702e-06</v>
       </c>
     </row>
     <row r="7">
@@ -716,7 +716,7 @@
         <v>0.08528155833482742</v>
       </c>
       <c r="K7" t="n">
-        <v>7.896299997810275e-06</v>
+        <v>5.511800001841038e-06</v>
       </c>
     </row>
     <row r="8">
@@ -757,7 +757,7 @@
         <v>0.09551058709621429</v>
       </c>
       <c r="K8" t="n">
-        <v>5.546200001845136e-06</v>
+        <v>5.616399997961708e-06</v>
       </c>
     </row>
     <row r="9">
@@ -798,7 +798,7 @@
         <v>0.09153081476688385</v>
       </c>
       <c r="K9" t="n">
-        <v>5.622199998470023e-06</v>
+        <v>5.272800000966526e-06</v>
       </c>
     </row>
     <row r="10">
@@ -839,7 +839,7 @@
         <v>0.09214134514331818</v>
       </c>
       <c r="K10" t="n">
-        <v>5.189500006963499e-06</v>
+        <v>5.558600008953362e-06</v>
       </c>
     </row>
     <row r="11">
@@ -880,7 +880,7 @@
         <v>0.1158287227153778</v>
       </c>
       <c r="K11" t="n">
-        <v>5.625499994494021e-06</v>
+        <v>5.603800003882498e-06</v>
       </c>
     </row>
     <row r="12">
@@ -921,7 +921,7 @@
         <v>0.1135990023612976</v>
       </c>
       <c r="K12" t="n">
-        <v>5.79979999747593e-06</v>
+        <v>5.445000002509914e-06</v>
       </c>
     </row>
     <row r="13">
@@ -962,7 +962,7 @@
         <v>0.03732327371835709</v>
       </c>
       <c r="K13" t="n">
-        <v>5.113099992740899e-06</v>
+        <v>5.181999993510544e-06</v>
       </c>
     </row>
     <row r="14">
@@ -1003,7 +1003,7 @@
         <v>0.03716478496789932</v>
       </c>
       <c r="K14" t="n">
-        <v>5.368300000554882e-06</v>
+        <v>5.928900005528704e-06</v>
       </c>
     </row>
     <row r="15">
@@ -1044,7 +1044,7 @@
         <v>0.03989281505346298</v>
       </c>
       <c r="K15" t="n">
-        <v>6.724100006977096e-06</v>
+        <v>5.51899999845773e-06</v>
       </c>
     </row>
     <row r="16">
@@ -1085,7 +1085,7 @@
         <v>0.03747523203492165</v>
       </c>
       <c r="K16" t="n">
-        <v>5.641099996864796e-06</v>
+        <v>7.117100001778453e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1126,7 +1126,7 @@
         <v>0.05985265970230103</v>
       </c>
       <c r="K17" t="n">
-        <v>6.653599994024261e-06</v>
+        <v>6.693699993775226e-06</v>
       </c>
     </row>
     <row r="18">
@@ -1167,7 +1167,7 @@
         <v>0.06427808851003647</v>
       </c>
       <c r="K18" t="n">
-        <v>6.860399997094646e-06</v>
+        <v>6.9392000004882e-06</v>
       </c>
     </row>
     <row r="19">
@@ -1208,7 +1208,7 @@
         <v>0.06141677126288414</v>
       </c>
       <c r="K19" t="n">
-        <v>6.0174999962328e-06</v>
+        <v>6.524399999761954e-06</v>
       </c>
     </row>
     <row r="20">
@@ -1249,7 +1249,7 @@
         <v>0.05974716320633888</v>
       </c>
       <c r="K20" t="n">
-        <v>6.070099989301525e-06</v>
+        <v>6.720699995639734e-06</v>
       </c>
     </row>
     <row r="21">
@@ -1290,7 +1290,7 @@
         <v>0.06122929230332375</v>
       </c>
       <c r="K21" t="n">
-        <v>5.940399991231971e-06</v>
+        <v>6.484000012278557e-06</v>
       </c>
     </row>
     <row r="22">
@@ -1331,7 +1331,7 @@
         <v>0.0472424142062664</v>
       </c>
       <c r="K22" t="n">
-        <v>5.804500004160218e-06</v>
+        <v>6.033899990143255e-06</v>
       </c>
     </row>
     <row r="23">
@@ -1372,7 +1372,7 @@
         <v>0.04826546832919121</v>
       </c>
       <c r="K23" t="n">
-        <v>5.851299996720627e-06</v>
+        <v>6.389800008037127e-06</v>
       </c>
     </row>
     <row r="24">
@@ -1413,7 +1413,7 @@
         <v>0.050253976136446</v>
       </c>
       <c r="K24" t="n">
-        <v>6.453699999838136e-06</v>
+        <v>8.006200005183928e-06</v>
       </c>
     </row>
     <row r="25">
@@ -1454,7 +1454,7 @@
         <v>0.04755860194563866</v>
       </c>
       <c r="K25" t="n">
-        <v>6.597199986572377e-06</v>
+        <v>6.254100007936358e-06</v>
       </c>
     </row>
     <row r="26">
@@ -1495,7 +1495,7 @@
         <v>0.04773597046732903</v>
       </c>
       <c r="K26" t="n">
-        <v>6.632499993429519e-06</v>
+        <v>6.732699999702163e-06</v>
       </c>
     </row>
     <row r="27">
@@ -1536,7 +1536,7 @@
         <v>1.020527601242065</v>
       </c>
       <c r="K27" t="n">
-        <v>7.106500008376315e-06</v>
+        <v>5.16329999663867e-06</v>
       </c>
     </row>
     <row r="28">
@@ -1577,7 +1577,130 @@
         <v>1.213654160499573</v>
       </c>
       <c r="K28" t="n">
-        <v>4.980800003977492e-06</v>
+        <v>4.823000010219403e-06</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ablated PINN</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Run 3</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>-854.43 (18.09)</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.05324763059616089</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.008193898946046829</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8.585378646850586</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.2405394017696381</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.011734247207642</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3.593719959259033</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.073970437049866</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.914099990855903e-06</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ablated PINN</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Run 4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>-804.93 (16.89)</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.05677470564842224</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.008175390772521496</v>
+      </c>
+      <c r="F30" t="n">
+        <v>8.155158042907715</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.2998057901859283</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.9377399682998657</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3.672524213790894</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.722495317459106</v>
+      </c>
+      <c r="K30" t="n">
+        <v>5.16270000662189e-06</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ablated PINN</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Run 5</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>-804.90 (16.92)</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.04412353038787842</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.006856582127511501</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8.172106742858887</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.3017652034759521</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.9365151524543762</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.672980070114136</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.727726340293884</v>
+      </c>
+      <c r="K31" t="n">
+        <v>5.172899996978231e-06</v>
       </c>
     </row>
   </sheetData>

--- a/14.xlsx
+++ b/14.xlsx
@@ -486,20 +486,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.76 (3.19)</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.621273040771484</v>
+        <v>1.507521145939827</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1203370690345764</v>
+        <v>0.1203370748758316</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1866598129272461</v>
+        <v>0.1376806048750877</v>
       </c>
       <c r="G2" t="n">
-        <v>0.008726411499083042</v>
+        <v>0.008726411801762878</v>
       </c>
       <c r="H2" t="n">
         <v>1.177233457565308</v>
@@ -511,7 +511,7 @@
         <v>0.06684777140617371</v>
       </c>
       <c r="K2" t="n">
-        <v>3.231809999851976e-05</v>
+        <v>9.493199999951684e-06</v>
       </c>
     </row>
     <row r="3">
@@ -527,20 +527,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.22 (3.20)</t>
+          <t>35.22</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.116897821426392</v>
+        <v>1.095649199485779</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1253170222043991</v>
+        <v>0.1253170286938548</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4395032525062561</v>
+        <v>0.4258854112923146</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03996847569942474</v>
+        <v>0.03996847586706281</v>
       </c>
       <c r="H3" t="n">
         <v>0.1991908848285675</v>
@@ -552,7 +552,7 @@
         <v>0.07220740616321564</v>
       </c>
       <c r="K3" t="n">
-        <v>5.294900009175762e-06</v>
+        <v>5.737400000043635e-06</v>
       </c>
     </row>
     <row r="4">
@@ -568,20 +568,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32.89 (3.15)</t>
+          <t>32.89</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.161139249801636</v>
+        <v>1.118135518312454</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1150936037302017</v>
+        <v>0.1150936045199633</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4398343563079834</v>
+        <v>0.4326098023653031</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04111042991280556</v>
+        <v>0.04111043306067586</v>
       </c>
       <c r="H4" t="n">
         <v>0.195774033665657</v>
@@ -593,7 +593,7 @@
         <v>0.0724397674202919</v>
       </c>
       <c r="K4" t="n">
-        <v>5.51820000691805e-06</v>
+        <v>5.629300000009608e-06</v>
       </c>
     </row>
     <row r="5">
@@ -609,20 +609,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-19.24 (1.93)</t>
+          <t>-19.24</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.722341775894165</v>
+        <v>0.6951915262341499</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1189694404602051</v>
+        <v>0.1189694488272071</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7214891910552979</v>
+        <v>0.7098399860262871</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07070331275463104</v>
+        <v>0.07070331577956676</v>
       </c>
       <c r="H5" t="n">
         <v>0.9304105639457703</v>
@@ -634,7 +634,7 @@
         <v>0.05048612505197525</v>
       </c>
       <c r="K5" t="n">
-        <v>7.407400000374764e-06</v>
+        <v>6.059899999854679e-06</v>
       </c>
     </row>
     <row r="6">
@@ -650,20 +650,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8.17 (2.69)</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1072748750448227</v>
+        <v>0.09126409647613763</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04408286884427071</v>
+        <v>0.04408286951109767</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0746159553527832</v>
+        <v>0.05881992936134339</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001048496924340725</v>
+        <v>0.001048496861942112</v>
       </c>
       <c r="H6" t="n">
         <v>1.187484502792358</v>
@@ -675,7 +675,7 @@
         <v>0.07279366999864578</v>
       </c>
       <c r="K6" t="n">
-        <v>5.736499995691702e-06</v>
+        <v>6.092599999874437e-06</v>
       </c>
     </row>
     <row r="7">
@@ -691,20 +691,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-38.74 (1.45)</t>
+          <t>-38.74</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9931461811065674</v>
+        <v>0.9850751592516899</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1250759959220886</v>
+        <v>0.1250760049149394</v>
       </c>
       <c r="F7" t="n">
-        <v>0.07963383197784424</v>
+        <v>0.07322988539934158</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004229052923619747</v>
+        <v>0.004229053039569408</v>
       </c>
       <c r="H7" t="n">
         <v>0.09441260993480682</v>
@@ -716,7 +716,7 @@
         <v>0.08528155833482742</v>
       </c>
       <c r="K7" t="n">
-        <v>5.511800001841038e-06</v>
+        <v>5.985899999814137e-06</v>
       </c>
     </row>
     <row r="8">
@@ -732,20 +732,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-32.66 (1.61)</t>
+          <t>-32.66</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.05359673500061</v>
+        <v>1.040643057465553</v>
       </c>
       <c r="E8" t="n">
-        <v>0.11422099173069</v>
+        <v>0.1142210026979446</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03472024202346802</v>
+        <v>0.02064226824045181</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001826123479986563</v>
+        <v>0.0001826123488135636</v>
       </c>
       <c r="H8" t="n">
         <v>0.07677828520536423</v>
@@ -757,7 +757,7 @@
         <v>0.09551058709621429</v>
       </c>
       <c r="K8" t="n">
-        <v>5.616399997961708e-06</v>
+        <v>7.176600000093458e-06</v>
       </c>
     </row>
     <row r="9">
@@ -773,20 +773,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-31.81 (1.62)</t>
+          <t>-31.81</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.068664789199829</v>
+        <v>1.050167424440384</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1134010180830956</v>
+        <v>0.1134010265246034</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01989829540252686</v>
+        <v>0.01230723243951798</v>
       </c>
       <c r="G9" t="n">
-        <v>9.615025192033499e-05</v>
+        <v>9.615025343373418e-05</v>
       </c>
       <c r="H9" t="n">
         <v>0.07427655905485153</v>
@@ -798,7 +798,7 @@
         <v>0.09153081476688385</v>
       </c>
       <c r="K9" t="n">
-        <v>5.272800000966526e-06</v>
+        <v>6.052000000181579e-06</v>
       </c>
     </row>
     <row r="10">
@@ -814,20 +814,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-32.96 (1.67)</t>
+          <t>-32.96</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.07895839214325</v>
+        <v>1.036805002570152</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1152711734175682</v>
+        <v>0.1152711741551757</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0432770848274231</v>
+        <v>0.02200803172588348</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0005507275345735252</v>
+        <v>0.0005507275266572833</v>
       </c>
       <c r="H10" t="n">
         <v>1.159277677536011</v>
@@ -839,7 +839,7 @@
         <v>0.09214134514331818</v>
       </c>
       <c r="K10" t="n">
-        <v>5.558600008953362e-06</v>
+        <v>6.227399999943372e-06</v>
       </c>
     </row>
     <row r="11">
@@ -855,20 +855,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-36.82 (1.55)</t>
+          <t>-36.82</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.06371545791626</v>
+        <v>1.03347943687439</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1208392605185509</v>
+        <v>0.120839244261384</v>
       </c>
       <c r="F11" t="n">
-        <v>0.06335258483886719</v>
+        <v>0.05863321894407272</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00205012084916234</v>
+        <v>0.00205012084543705</v>
       </c>
       <c r="H11" t="n">
         <v>0.084022156894207</v>
@@ -880,7 +880,7 @@
         <v>0.1158287227153778</v>
       </c>
       <c r="K11" t="n">
-        <v>5.603800003882498e-06</v>
+        <v>6.466999999929612e-06</v>
       </c>
     </row>
     <row r="12">
@@ -896,20 +896,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-9.68 (2.15)</t>
+          <t>-9.68</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.434185385704041</v>
+        <v>1.416134194135666</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2699629366397858</v>
+        <v>0.2699629244208336</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8818920850753784</v>
+        <v>0.8815997189879418</v>
       </c>
       <c r="G12" t="n">
-        <v>0.09621918946504593</v>
+        <v>0.09621919107437134</v>
       </c>
       <c r="H12" t="n">
         <v>0.6152425408363342</v>
@@ -921,7 +921,7 @@
         <v>0.1135990023612976</v>
       </c>
       <c r="K12" t="n">
-        <v>5.445000002509914e-06</v>
+        <v>6.313099999943006e-06</v>
       </c>
     </row>
     <row r="13">
@@ -937,20 +937,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.40 (3.26)</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9.642556190490723</v>
+        <v>9.318998808860778</v>
       </c>
       <c r="E13" t="n">
-        <v>1.864211440086365</v>
+        <v>1.864211428999901</v>
       </c>
       <c r="F13" t="n">
-        <v>19.41717338562012</v>
+        <v>15.0870366191864</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4467650353908539</v>
+        <v>0.4467650509476662</v>
       </c>
       <c r="H13" t="n">
         <v>0.4047165811061859</v>
@@ -962,7 +962,7 @@
         <v>0.03732327371835709</v>
       </c>
       <c r="K13" t="n">
-        <v>5.181999993510544e-06</v>
+        <v>6.168099999968035e-06</v>
       </c>
     </row>
     <row r="14">
@@ -978,20 +978,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.39 (3.27)</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>9.766969680786133</v>
+        <v>9.402688475608826</v>
       </c>
       <c r="E14" t="n">
-        <v>1.874432563781738</v>
+        <v>1.874432633042336</v>
       </c>
       <c r="F14" t="n">
-        <v>20.11959266662598</v>
+        <v>15.10329270839691</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4530208706855774</v>
+        <v>0.4530208821296692</v>
       </c>
       <c r="H14" t="n">
         <v>0.4066689312458038</v>
@@ -1003,7 +1003,7 @@
         <v>0.03716478496789932</v>
       </c>
       <c r="K14" t="n">
-        <v>5.928900005528704e-06</v>
+        <v>1.335560000006808e-05</v>
       </c>
     </row>
     <row r="15">
@@ -1019,20 +1019,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.39 (3.28)</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>9.508668899536133</v>
+        <v>9.141275308609009</v>
       </c>
       <c r="E15" t="n">
-        <v>1.847036600112915</v>
+        <v>1.84703670156002</v>
       </c>
       <c r="F15" t="n">
-        <v>17.18930244445801</v>
+        <v>14.08442363357544</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5236369371414185</v>
+        <v>0.5236369768381118</v>
       </c>
       <c r="H15" t="n">
         <v>0.3738998472690582</v>
@@ -1044,7 +1044,7 @@
         <v>0.03989281505346298</v>
       </c>
       <c r="K15" t="n">
-        <v>5.51899999845773e-06</v>
+        <v>1.336839999999029e-05</v>
       </c>
     </row>
     <row r="16">
@@ -1060,20 +1060,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.40 (3.27)</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>9.494917869567871</v>
+        <v>9.177847730636596</v>
       </c>
       <c r="E16" t="n">
-        <v>1.861482620239258</v>
+        <v>1.861482509493828</v>
       </c>
       <c r="F16" t="n">
-        <v>17.30372619628906</v>
+        <v>13.84695748519897</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5127214789390564</v>
+        <v>0.5127214749455452</v>
       </c>
       <c r="H16" t="n">
         <v>0.3749077022075653</v>
@@ -1085,7 +1085,7 @@
         <v>0.03747523203492165</v>
       </c>
       <c r="K16" t="n">
-        <v>7.117100001778453e-06</v>
+        <v>1.318229999992582e-05</v>
       </c>
     </row>
     <row r="17">
@@ -1101,14 +1101,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6.02 (3.27)</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.769737720489502</v>
+        <v>1.704965883612633</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1910399496555328</v>
+        <v>0.1910399603992701</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1126,7 +1126,7 @@
         <v>0.05985265970230103</v>
       </c>
       <c r="K17" t="n">
-        <v>6.693699993775226e-06</v>
+        <v>1.476920000004611e-05</v>
       </c>
     </row>
     <row r="18">
@@ -1142,14 +1142,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6.08 (3.25)</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.179211854934692</v>
+        <v>1.13184225165844</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1816953271627426</v>
+        <v>0.1816953220367432</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1167,7 +1167,7 @@
         <v>0.06427808851003647</v>
       </c>
       <c r="K18" t="n">
-        <v>6.9392000004882e-06</v>
+        <v>1.56402000000071e-05</v>
       </c>
     </row>
     <row r="19">
@@ -1183,14 +1183,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6.18 (3.27)</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.229702472686768</v>
+        <v>1.944985589981079</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2022121101617813</v>
+        <v>0.2022121175080538</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1208,7 +1208,7 @@
         <v>0.06141677126288414</v>
       </c>
       <c r="K19" t="n">
-        <v>6.524399999761954e-06</v>
+        <v>1.542939999990267e-05</v>
       </c>
     </row>
     <row r="20">
@@ -1224,14 +1224,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5.97 (3.27)</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.57392954826355</v>
+        <v>1.436445544600487</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1798264980316162</v>
+        <v>0.1798265022188425</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1249,7 +1249,7 @@
         <v>0.05974716320633888</v>
       </c>
       <c r="K20" t="n">
-        <v>6.720699995639734e-06</v>
+        <v>1.560960000006162e-05</v>
       </c>
     </row>
     <row r="21">
@@ -1265,14 +1265,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6.04 (3.26)</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.303850173950195</v>
+        <v>5.079327826976776</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4743886291980743</v>
+        <v>0.4743886026442051</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
         <v>0.06122929230332375</v>
       </c>
       <c r="K21" t="n">
-        <v>6.484000012278557e-06</v>
+        <v>1.598139999987325e-05</v>
       </c>
     </row>
     <row r="22">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9.34 (2.61)</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.2656935453414917</v>
+        <v>0.249610868498683</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06127967685461044</v>
+        <v>0.06127967816591263</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02982461452484131</v>
+        <v>0.02700034844875336</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0006705671548843384</v>
+        <v>0.0006705671008676291</v>
       </c>
       <c r="H22" t="n">
         <v>0.0629999190568924</v>
@@ -1331,7 +1331,7 @@
         <v>0.0472424142062664</v>
       </c>
       <c r="K22" t="n">
-        <v>6.033899990143255e-06</v>
+        <v>1.564379999990706e-05</v>
       </c>
     </row>
     <row r="23">
@@ -1347,20 +1347,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11.68 (2.66)</t>
+          <t>11.68</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.4256680309772491</v>
+        <v>0.3588118672966957</v>
       </c>
       <c r="E23" t="n">
-        <v>0.07536008208990097</v>
+        <v>0.07536008327454329</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0310291051864624</v>
+        <v>0.02798840153217316</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0007254909141920507</v>
+        <v>0.0007254908950999379</v>
       </c>
       <c r="H23" t="n">
         <v>0.06363289803266525</v>
@@ -1372,7 +1372,7 @@
         <v>0.04826546832919121</v>
       </c>
       <c r="K23" t="n">
-        <v>6.389800008037127e-06</v>
+        <v>1.719850000017687e-05</v>
       </c>
     </row>
     <row r="24">
@@ -1388,20 +1388,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.25 (2.52)</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.3833224773406982</v>
+        <v>0.3503062247335911</v>
       </c>
       <c r="E24" t="n">
-        <v>0.07651928812265396</v>
+        <v>0.07651928365975619</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02307343482971191</v>
+        <v>0.02270333027839661</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0002378217614023015</v>
+        <v>0.0002378217522054911</v>
       </c>
       <c r="H24" t="n">
         <v>0.06166854873299599</v>
@@ -1413,7 +1413,7 @@
         <v>0.050253976136446</v>
       </c>
       <c r="K24" t="n">
-        <v>8.006200005183928e-06</v>
+        <v>1.573119999989103e-05</v>
       </c>
     </row>
     <row r="25">
@@ -1429,20 +1429,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>9.26 (2.61)</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.256565272808075</v>
+        <v>0.1967392119169235</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05876800417900085</v>
+        <v>0.05876800472661853</v>
       </c>
       <c r="F25" t="n">
-        <v>0.03172695636749268</v>
+        <v>0.02821539390087128</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0007930694846436381</v>
+        <v>0.0007930694688111544</v>
       </c>
       <c r="H25" t="n">
         <v>0.06216241419315338</v>
@@ -1454,7 +1454,7 @@
         <v>0.04755860194563866</v>
       </c>
       <c r="K25" t="n">
-        <v>6.254100007936358e-06</v>
+        <v>1.607519999993201e-05</v>
       </c>
     </row>
     <row r="26">
@@ -1470,20 +1470,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>10.12 (2.63)</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.2292059659957886</v>
+        <v>0.2072021725326776</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06516785174608231</v>
+        <v>0.06516785292327404</v>
       </c>
       <c r="F26" t="n">
-        <v>0.02794837951660156</v>
+        <v>0.02550696766376495</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0007351519307121634</v>
+        <v>0.000735151925124228</v>
       </c>
       <c r="H26" t="n">
         <v>0.06298694759607315</v>
@@ -1495,7 +1495,7 @@
         <v>0.04773597046732903</v>
       </c>
       <c r="K26" t="n">
-        <v>6.732699999702163e-06</v>
+        <v>1.58801999998559e-05</v>
       </c>
     </row>
     <row r="27">
@@ -1511,20 +1511,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-862.21 (18.28)</t>
+          <t>-862.21</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.04733014106750488</v>
+        <v>0.0351001445800066</v>
       </c>
       <c r="E27" t="n">
-        <v>0.007503214292228222</v>
+        <v>0.007503213917370886</v>
       </c>
       <c r="F27" t="n">
-        <v>8.668375968933105</v>
+        <v>8.615534524917603</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2386341094970703</v>
+        <v>0.2386340961754322</v>
       </c>
       <c r="H27" t="n">
         <v>1.028512477874756</v>
@@ -1536,7 +1536,7 @@
         <v>1.020527601242065</v>
       </c>
       <c r="K27" t="n">
-        <v>5.16329999663867e-06</v>
+        <v>1.685350000002472e-05</v>
       </c>
     </row>
     <row r="28">
@@ -1552,20 +1552,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-279.66 (4.74)</t>
+          <t>-279.66</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.0707341730594635</v>
+        <v>0.05382232209295034</v>
       </c>
       <c r="E28" t="n">
-        <v>0.01563688926398754</v>
+        <v>0.01563689017668366</v>
       </c>
       <c r="F28" t="n">
-        <v>3.134171009063721</v>
+        <v>2.926100548267364</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1762083172798157</v>
+        <v>0.176208320364356</v>
       </c>
       <c r="H28" t="n">
         <v>0.8491321206092834</v>
@@ -1577,7 +1577,7 @@
         <v>1.213654160499573</v>
       </c>
       <c r="K28" t="n">
-        <v>4.823000010219403e-06</v>
+        <v>1.338980000014089e-05</v>
       </c>
     </row>
     <row r="29">
@@ -1593,20 +1593,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-854.43 (18.09)</t>
+          <t>-854.43</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.05324763059616089</v>
+        <v>0.04216732012853026</v>
       </c>
       <c r="E29" t="n">
-        <v>0.008193898946046829</v>
+        <v>0.008193898860830814</v>
       </c>
       <c r="F29" t="n">
-        <v>8.585378646850586</v>
+        <v>8.546283812522889</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2405394017696381</v>
+        <v>0.2405394058525562</v>
       </c>
       <c r="H29" t="n">
         <v>1.011734247207642</v>
@@ -1618,7 +1618,7 @@
         <v>1.073970437049866</v>
       </c>
       <c r="K29" t="n">
-        <v>4.914099990855903e-06</v>
+        <v>1.219339999988733e-05</v>
       </c>
     </row>
     <row r="30">
@@ -1634,20 +1634,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-804.93 (16.89)</t>
+          <t>-804.93</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.05677470564842224</v>
+        <v>0.03068075277656317</v>
       </c>
       <c r="E30" t="n">
-        <v>0.008175390772521496</v>
+        <v>0.008175390501040965</v>
       </c>
       <c r="F30" t="n">
-        <v>8.155158042907715</v>
+        <v>8.108450738906861</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2998057901859283</v>
+        <v>0.2998057978749275</v>
       </c>
       <c r="H30" t="n">
         <v>0.9377399682998657</v>
@@ -1659,7 +1659,7 @@
         <v>1.722495317459106</v>
       </c>
       <c r="K30" t="n">
-        <v>5.16270000662189e-06</v>
+        <v>1.355689999991228e-05</v>
       </c>
     </row>
     <row r="31">
@@ -1675,20 +1675,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-804.90 (16.92)</t>
+          <t>-804.90</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.04412353038787842</v>
+        <v>0.03261048006638884</v>
       </c>
       <c r="E31" t="n">
-        <v>0.006856582127511501</v>
+        <v>0.006856581707950681</v>
       </c>
       <c r="F31" t="n">
-        <v>8.172106742858887</v>
+        <v>8.108305682182312</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3017652034759521</v>
+        <v>0.3017651666998863</v>
       </c>
       <c r="H31" t="n">
         <v>0.9365151524543762</v>
@@ -1700,7 +1700,7 @@
         <v>1.727726340293884</v>
       </c>
       <c r="K31" t="n">
-        <v>5.172899996978231e-06</v>
+        <v>1.228949999995166e-05</v>
       </c>
     </row>
   </sheetData>

--- a/14.xlsx
+++ b/14.xlsx
@@ -511,7 +511,7 @@
         <v>0.06684777140617371</v>
       </c>
       <c r="K2" t="n">
-        <v>9.493199999951684e-06</v>
+        <v>1.04186999999456e-05</v>
       </c>
     </row>
     <row r="3">
@@ -552,7 +552,7 @@
         <v>0.07220740616321564</v>
       </c>
       <c r="K3" t="n">
-        <v>5.737400000043635e-06</v>
+        <v>6.946100000050137e-06</v>
       </c>
     </row>
     <row r="4">
@@ -593,7 +593,7 @@
         <v>0.0724397674202919</v>
       </c>
       <c r="K4" t="n">
-        <v>5.629300000009608e-06</v>
+        <v>6.117800000083662e-06</v>
       </c>
     </row>
     <row r="5">
@@ -634,7 +634,7 @@
         <v>0.05048612505197525</v>
       </c>
       <c r="K5" t="n">
-        <v>6.059899999854679e-06</v>
+        <v>7.526199999801975e-06</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +675,7 @@
         <v>0.07279366999864578</v>
       </c>
       <c r="K6" t="n">
-        <v>6.092599999874437e-06</v>
+        <v>6.707900000037626e-06</v>
       </c>
     </row>
     <row r="7">
@@ -716,7 +716,7 @@
         <v>0.08528155833482742</v>
       </c>
       <c r="K7" t="n">
-        <v>5.985899999814137e-06</v>
+        <v>6.504399999812449e-06</v>
       </c>
     </row>
     <row r="8">
@@ -757,7 +757,7 @@
         <v>0.09551058709621429</v>
       </c>
       <c r="K8" t="n">
-        <v>7.176600000093458e-06</v>
+        <v>8.959900000036214e-06</v>
       </c>
     </row>
     <row r="9">
@@ -798,7 +798,7 @@
         <v>0.09153081476688385</v>
       </c>
       <c r="K9" t="n">
-        <v>6.052000000181579e-06</v>
+        <v>7.031899999901725e-06</v>
       </c>
     </row>
     <row r="10">
@@ -839,7 +839,7 @@
         <v>0.09214134514331818</v>
       </c>
       <c r="K10" t="n">
-        <v>6.227399999943372e-06</v>
+        <v>7.362900000089212e-06</v>
       </c>
     </row>
     <row r="11">
@@ -880,7 +880,7 @@
         <v>0.1158287227153778</v>
       </c>
       <c r="K11" t="n">
-        <v>6.466999999929612e-06</v>
+        <v>7.022600000027524e-06</v>
       </c>
     </row>
     <row r="12">
@@ -921,7 +921,7 @@
         <v>0.1135990023612976</v>
       </c>
       <c r="K12" t="n">
-        <v>6.313099999943006e-06</v>
+        <v>6.851600000118196e-06</v>
       </c>
     </row>
     <row r="13">
@@ -962,7 +962,7 @@
         <v>0.03732327371835709</v>
       </c>
       <c r="K13" t="n">
-        <v>6.168099999968035e-06</v>
+        <v>9.807099999989078e-06</v>
       </c>
     </row>
     <row r="14">
@@ -1003,7 +1003,7 @@
         <v>0.03716478496789932</v>
       </c>
       <c r="K14" t="n">
-        <v>1.335560000006808e-05</v>
+        <v>6.956500000114829e-06</v>
       </c>
     </row>
     <row r="15">
@@ -1044,7 +1044,7 @@
         <v>0.03989281505346298</v>
       </c>
       <c r="K15" t="n">
-        <v>1.336839999999029e-05</v>
+        <v>6.995799999913288e-06</v>
       </c>
     </row>
     <row r="16">
@@ -1085,7 +1085,7 @@
         <v>0.03747523203492165</v>
       </c>
       <c r="K16" t="n">
-        <v>1.318229999992582e-05</v>
+        <v>7.355400000051304e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1126,7 +1126,7 @@
         <v>0.05985265970230103</v>
       </c>
       <c r="K17" t="n">
-        <v>1.476920000004611e-05</v>
+        <v>1.020949999997356e-05</v>
       </c>
     </row>
     <row r="18">
@@ -1167,7 +1167,7 @@
         <v>0.06427808851003647</v>
       </c>
       <c r="K18" t="n">
-        <v>1.56402000000071e-05</v>
+        <v>8.725800000092932e-06</v>
       </c>
     </row>
     <row r="19">
@@ -1208,7 +1208,7 @@
         <v>0.06141677126288414</v>
       </c>
       <c r="K19" t="n">
-        <v>1.542939999990267e-05</v>
+        <v>8.258300000079543e-06</v>
       </c>
     </row>
     <row r="20">
@@ -1249,7 +1249,7 @@
         <v>0.05974716320633888</v>
       </c>
       <c r="K20" t="n">
-        <v>1.560960000006162e-05</v>
+        <v>8.552600000029997e-06</v>
       </c>
     </row>
     <row r="21">
@@ -1290,7 +1290,7 @@
         <v>0.06122929230332375</v>
       </c>
       <c r="K21" t="n">
-        <v>1.598139999987325e-05</v>
+        <v>8.42600000009952e-06</v>
       </c>
     </row>
     <row r="22">
@@ -1331,7 +1331,7 @@
         <v>0.0472424142062664</v>
       </c>
       <c r="K22" t="n">
-        <v>1.564379999990706e-05</v>
+        <v>9.380699999837817e-06</v>
       </c>
     </row>
     <row r="23">
@@ -1372,7 +1372,7 @@
         <v>0.04826546832919121</v>
       </c>
       <c r="K23" t="n">
-        <v>1.719850000017687e-05</v>
+        <v>1.067420000003949e-05</v>
       </c>
     </row>
     <row r="24">
@@ -1413,7 +1413,7 @@
         <v>0.050253976136446</v>
       </c>
       <c r="K24" t="n">
-        <v>1.573119999989103e-05</v>
+        <v>8.853799999997137e-06</v>
       </c>
     </row>
     <row r="25">
@@ -1454,7 +1454,7 @@
         <v>0.04755860194563866</v>
       </c>
       <c r="K25" t="n">
-        <v>1.607519999993201e-05</v>
+        <v>7.976599999892641e-06</v>
       </c>
     </row>
     <row r="26">
@@ -1495,7 +1495,7 @@
         <v>0.04773597046732903</v>
       </c>
       <c r="K26" t="n">
-        <v>1.58801999998559e-05</v>
+        <v>9.112899999990986e-06</v>
       </c>
     </row>
     <row r="27">
@@ -1536,7 +1536,7 @@
         <v>1.020527601242065</v>
       </c>
       <c r="K27" t="n">
-        <v>1.685350000002472e-05</v>
+        <v>5.996800000048097e-06</v>
       </c>
     </row>
     <row r="28">
@@ -1577,7 +1577,7 @@
         <v>1.213654160499573</v>
       </c>
       <c r="K28" t="n">
-        <v>1.338980000014089e-05</v>
+        <v>6.301500000063243e-06</v>
       </c>
     </row>
     <row r="29">
@@ -1618,7 +1618,7 @@
         <v>1.073970437049866</v>
       </c>
       <c r="K29" t="n">
-        <v>1.219339999988733e-05</v>
+        <v>5.857099999957427e-06</v>
       </c>
     </row>
     <row r="30">
@@ -1659,7 +1659,7 @@
         <v>1.722495317459106</v>
       </c>
       <c r="K30" t="n">
-        <v>1.355689999991228e-05</v>
+        <v>6.437200000164012e-06</v>
       </c>
     </row>
     <row r="31">
@@ -1700,7 +1700,7 @@
         <v>1.727726340293884</v>
       </c>
       <c r="K31" t="n">
-        <v>1.228949999995166e-05</v>
+        <v>6.972700000005716e-06</v>
       </c>
     </row>
   </sheetData>

--- a/14.xlsx
+++ b/14.xlsx
@@ -486,20 +486,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.76 (3.19)</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.507521145939827</v>
+        <v>1.621273040771484</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1203370748758316</v>
+        <v>0.1203370690345764</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1376806048750877</v>
+        <v>0.1866598129272461</v>
       </c>
       <c r="G2" t="n">
-        <v>0.008726411801762878</v>
+        <v>0.008726411499083042</v>
       </c>
       <c r="H2" t="n">
         <v>1.177233457565308</v>
@@ -511,7 +511,7 @@
         <v>0.06684777140617371</v>
       </c>
       <c r="K2" t="n">
-        <v>1.04186999999456e-05</v>
+        <v>1.308379999682074e-05</v>
       </c>
     </row>
     <row r="3">
@@ -527,20 +527,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.22</t>
+          <t>35.22 (3.20)</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.095649199485779</v>
+        <v>1.116897821426392</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1253170286938548</v>
+        <v>0.1253170222043991</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4258854112923146</v>
+        <v>0.4395032525062561</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03996847586706281</v>
+        <v>0.03996847569942474</v>
       </c>
       <c r="H3" t="n">
         <v>0.1991908848285675</v>
@@ -552,7 +552,7 @@
         <v>0.07220740616321564</v>
       </c>
       <c r="K3" t="n">
-        <v>6.946100000050137e-06</v>
+        <v>5.219000006036367e-06</v>
       </c>
     </row>
     <row r="4">
@@ -568,20 +568,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32.89</t>
+          <t>32.89 (3.15)</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.118135518312454</v>
+        <v>1.161139249801636</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1150936045199633</v>
+        <v>0.1150936037302017</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4326098023653031</v>
+        <v>0.4398343563079834</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04111043306067586</v>
+        <v>0.04111042991280556</v>
       </c>
       <c r="H4" t="n">
         <v>0.195774033665657</v>
@@ -593,7 +593,7 @@
         <v>0.0724397674202919</v>
       </c>
       <c r="K4" t="n">
-        <v>6.117800000083662e-06</v>
+        <v>5.549699999392032e-06</v>
       </c>
     </row>
     <row r="5">
@@ -609,20 +609,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-19.24</t>
+          <t>-19.24 (1.93)</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.6951915262341499</v>
+        <v>0.722341775894165</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1189694488272071</v>
+        <v>0.1189694404602051</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7098399860262871</v>
+        <v>0.7214891910552979</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07070331577956676</v>
+        <v>0.07070331275463104</v>
       </c>
       <c r="H5" t="n">
         <v>0.9304105639457703</v>
@@ -634,7 +634,7 @@
         <v>0.05048612505197525</v>
       </c>
       <c r="K5" t="n">
-        <v>7.526199999801975e-06</v>
+        <v>7.174999998824206e-06</v>
       </c>
     </row>
     <row r="6">
@@ -650,20 +650,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>8.17 (2.69)</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.09126409647613763</v>
+        <v>0.1072748750448227</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04408286951109767</v>
+        <v>0.04408286884427071</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05881992936134339</v>
+        <v>0.0746159553527832</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001048496861942112</v>
+        <v>0.001048496924340725</v>
       </c>
       <c r="H6" t="n">
         <v>1.187484502792358</v>
@@ -675,7 +675,7 @@
         <v>0.07279366999864578</v>
       </c>
       <c r="K6" t="n">
-        <v>6.707900000037626e-06</v>
+        <v>7.185200003732461e-06</v>
       </c>
     </row>
     <row r="7">
@@ -691,20 +691,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-38.74</t>
+          <t>-38.74 (1.45)</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9850751592516899</v>
+        <v>0.9931461811065674</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1250760049149394</v>
+        <v>0.1250759959220886</v>
       </c>
       <c r="F7" t="n">
-        <v>0.07322988539934158</v>
+        <v>0.07963383197784424</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004229053039569408</v>
+        <v>0.004229052923619747</v>
       </c>
       <c r="H7" t="n">
         <v>0.09441260993480682</v>
@@ -716,7 +716,7 @@
         <v>0.08528155833482742</v>
       </c>
       <c r="K7" t="n">
-        <v>6.504399999812449e-06</v>
+        <v>5.321700002241414e-06</v>
       </c>
     </row>
     <row r="8">
@@ -732,20 +732,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-32.66</t>
+          <t>-32.66 (1.61)</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.040643057465553</v>
+        <v>1.05359673500061</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1142210026979446</v>
+        <v>0.11422099173069</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02064226824045181</v>
+        <v>0.03472024202346802</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001826123488135636</v>
+        <v>0.0001826123479986563</v>
       </c>
       <c r="H8" t="n">
         <v>0.07677828520536423</v>
@@ -757,7 +757,7 @@
         <v>0.09551058709621429</v>
       </c>
       <c r="K8" t="n">
-        <v>8.959900000036214e-06</v>
+        <v>6.41939999331953e-06</v>
       </c>
     </row>
     <row r="9">
@@ -773,20 +773,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-31.81</t>
+          <t>-31.81 (1.62)</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.050167424440384</v>
+        <v>1.068664789199829</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1134010265246034</v>
+        <v>0.1134010180830956</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01230723243951798</v>
+        <v>0.01989829540252686</v>
       </c>
       <c r="G9" t="n">
-        <v>9.615025343373418e-05</v>
+        <v>9.615025192033499e-05</v>
       </c>
       <c r="H9" t="n">
         <v>0.07427655905485153</v>
@@ -798,7 +798,7 @@
         <v>0.09153081476688385</v>
       </c>
       <c r="K9" t="n">
-        <v>7.031899999901725e-06</v>
+        <v>5.750200005422812e-06</v>
       </c>
     </row>
     <row r="10">
@@ -814,20 +814,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-32.96</t>
+          <t>-32.96 (1.67)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.036805002570152</v>
+        <v>1.07895839214325</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1152711741551757</v>
+        <v>0.1152711734175682</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02200803172588348</v>
+        <v>0.0432770848274231</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0005507275266572833</v>
+        <v>0.0005507275345735252</v>
       </c>
       <c r="H10" t="n">
         <v>1.159277677536011</v>
@@ -839,7 +839,7 @@
         <v>0.09214134514331818</v>
       </c>
       <c r="K10" t="n">
-        <v>7.362900000089212e-06</v>
+        <v>6.069899995054584e-06</v>
       </c>
     </row>
     <row r="11">
@@ -855,20 +855,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-36.82</t>
+          <t>-36.82 (1.55)</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.03347943687439</v>
+        <v>1.06371545791626</v>
       </c>
       <c r="E11" t="n">
-        <v>0.120839244261384</v>
+        <v>0.1208392605185509</v>
       </c>
       <c r="F11" t="n">
-        <v>0.05863321894407272</v>
+        <v>0.06335258483886719</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00205012084543705</v>
+        <v>0.00205012084916234</v>
       </c>
       <c r="H11" t="n">
         <v>0.084022156894207</v>
@@ -880,7 +880,7 @@
         <v>0.1158287227153778</v>
       </c>
       <c r="K11" t="n">
-        <v>7.022600000027524e-06</v>
+        <v>6.341000000247732e-06</v>
       </c>
     </row>
     <row r="12">
@@ -896,20 +896,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-9.68</t>
+          <t>-9.68 (2.15)</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.416134194135666</v>
+        <v>1.434185385704041</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2699629244208336</v>
+        <v>0.2699629366397858</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8815997189879418</v>
+        <v>0.8818920850753784</v>
       </c>
       <c r="G12" t="n">
-        <v>0.09621919107437134</v>
+        <v>0.09621918946504593</v>
       </c>
       <c r="H12" t="n">
         <v>0.6152425408363342</v>
@@ -921,7 +921,7 @@
         <v>0.1135990023612976</v>
       </c>
       <c r="K12" t="n">
-        <v>6.851600000118196e-06</v>
+        <v>5.552099995838944e-06</v>
       </c>
     </row>
     <row r="13">
@@ -937,20 +937,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.40 (3.26)</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9.318998808860778</v>
+        <v>9.642556190490723</v>
       </c>
       <c r="E13" t="n">
-        <v>1.864211428999901</v>
+        <v>1.864211440086365</v>
       </c>
       <c r="F13" t="n">
-        <v>15.0870366191864</v>
+        <v>19.41717338562012</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4467650509476662</v>
+        <v>0.4467650353908539</v>
       </c>
       <c r="H13" t="n">
         <v>0.4047165811061859</v>
@@ -962,7 +962,7 @@
         <v>0.03732327371835709</v>
       </c>
       <c r="K13" t="n">
-        <v>9.807099999989078e-06</v>
+        <v>5.686399999831337e-06</v>
       </c>
     </row>
     <row r="14">
@@ -978,20 +978,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.39 (3.27)</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>9.402688475608826</v>
+        <v>9.766969680786133</v>
       </c>
       <c r="E14" t="n">
-        <v>1.874432633042336</v>
+        <v>1.874432563781738</v>
       </c>
       <c r="F14" t="n">
-        <v>15.10329270839691</v>
+        <v>20.11959266662598</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4530208821296692</v>
+        <v>0.4530208706855774</v>
       </c>
       <c r="H14" t="n">
         <v>0.4066689312458038</v>
@@ -1003,7 +1003,7 @@
         <v>0.03716478496789932</v>
       </c>
       <c r="K14" t="n">
-        <v>6.956500000114829e-06</v>
+        <v>5.759599996963516e-06</v>
       </c>
     </row>
     <row r="15">
@@ -1019,20 +1019,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.39 (3.28)</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>9.141275308609009</v>
+        <v>9.508668899536133</v>
       </c>
       <c r="E15" t="n">
-        <v>1.84703670156002</v>
+        <v>1.847036600112915</v>
       </c>
       <c r="F15" t="n">
-        <v>14.08442363357544</v>
+        <v>17.18930244445801</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5236369768381118</v>
+        <v>0.5236369371414185</v>
       </c>
       <c r="H15" t="n">
         <v>0.3738998472690582</v>
@@ -1044,7 +1044,7 @@
         <v>0.03989281505346298</v>
       </c>
       <c r="K15" t="n">
-        <v>6.995799999913288e-06</v>
+        <v>6.512400002975482e-06</v>
       </c>
     </row>
     <row r="16">
@@ -1060,20 +1060,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.40 (3.27)</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>9.177847730636596</v>
+        <v>9.494917869567871</v>
       </c>
       <c r="E16" t="n">
-        <v>1.861482509493828</v>
+        <v>1.861482620239258</v>
       </c>
       <c r="F16" t="n">
-        <v>13.84695748519897</v>
+        <v>17.30372619628906</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5127214749455452</v>
+        <v>0.5127214789390564</v>
       </c>
       <c r="H16" t="n">
         <v>0.3749077022075653</v>
@@ -1085,7 +1085,7 @@
         <v>0.03747523203492165</v>
       </c>
       <c r="K16" t="n">
-        <v>7.355400000051304e-06</v>
+        <v>7.840299993404187e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1101,14 +1101,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.02 (3.27)</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.704965883612633</v>
+        <v>1.769737720489502</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1910399603992701</v>
+        <v>0.1910399496555328</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1126,7 +1126,7 @@
         <v>0.05985265970230103</v>
       </c>
       <c r="K17" t="n">
-        <v>1.020949999997356e-05</v>
+        <v>7.258700003148988e-06</v>
       </c>
     </row>
     <row r="18">
@@ -1142,14 +1142,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.08 (3.25)</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.13184225165844</v>
+        <v>1.179211854934692</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1816953220367432</v>
+        <v>0.1816953271627426</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1167,7 +1167,7 @@
         <v>0.06427808851003647</v>
       </c>
       <c r="K18" t="n">
-        <v>8.725800000092932e-06</v>
+        <v>7.395499997073785e-06</v>
       </c>
     </row>
     <row r="19">
@@ -1183,14 +1183,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.18 (3.27)</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.944985589981079</v>
+        <v>2.229702472686768</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2022121175080538</v>
+        <v>0.2022121101617813</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1208,7 +1208,7 @@
         <v>0.06141677126288414</v>
       </c>
       <c r="K19" t="n">
-        <v>8.258300000079543e-06</v>
+        <v>6.576799998583737e-06</v>
       </c>
     </row>
     <row r="20">
@@ -1224,14 +1224,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.97 (3.27)</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.436445544600487</v>
+        <v>1.57392954826355</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1798265022188425</v>
+        <v>0.1798264980316162</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1249,7 +1249,7 @@
         <v>0.05974716320633888</v>
       </c>
       <c r="K20" t="n">
-        <v>8.552600000029997e-06</v>
+        <v>7.170400000177324e-06</v>
       </c>
     </row>
     <row r="21">
@@ -1265,14 +1265,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.04 (3.26)</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.079327826976776</v>
+        <v>5.303850173950195</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4743886026442051</v>
+        <v>0.4743886291980743</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
         <v>0.06122929230332375</v>
       </c>
       <c r="K21" t="n">
-        <v>8.42600000009952e-06</v>
+        <v>6.737799994880334e-06</v>
       </c>
     </row>
     <row r="22">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>9.34 (2.61)</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.249610868498683</v>
+        <v>0.2656935453414917</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06127967816591263</v>
+        <v>0.06127967685461044</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02700034844875336</v>
+        <v>0.02982461452484131</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0006705671008676291</v>
+        <v>0.0006705671548843384</v>
       </c>
       <c r="H22" t="n">
         <v>0.0629999190568924</v>
@@ -1331,7 +1331,7 @@
         <v>0.0472424142062664</v>
       </c>
       <c r="K22" t="n">
-        <v>9.380699999837817e-06</v>
+        <v>7.789099996443839e-06</v>
       </c>
     </row>
     <row r="23">
@@ -1347,20 +1347,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>11.68 (2.66)</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.3588118672966957</v>
+        <v>0.4256680309772491</v>
       </c>
       <c r="E23" t="n">
-        <v>0.07536008327454329</v>
+        <v>0.07536008208990097</v>
       </c>
       <c r="F23" t="n">
-        <v>0.02798840153217316</v>
+        <v>0.0310291051864624</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0007254908950999379</v>
+        <v>0.0007254909141920507</v>
       </c>
       <c r="H23" t="n">
         <v>0.06363289803266525</v>
@@ -1372,7 +1372,7 @@
         <v>0.04826546832919121</v>
       </c>
       <c r="K23" t="n">
-        <v>1.067420000003949e-05</v>
+        <v>6.846100004622712e-06</v>
       </c>
     </row>
     <row r="24">
@@ -1388,20 +1388,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.25 (2.52)</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.3503062247335911</v>
+        <v>0.3833224773406982</v>
       </c>
       <c r="E24" t="n">
-        <v>0.07651928365975619</v>
+        <v>0.07651928812265396</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02270333027839661</v>
+        <v>0.02307343482971191</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0002378217522054911</v>
+        <v>0.0002378217614023015</v>
       </c>
       <c r="H24" t="n">
         <v>0.06166854873299599</v>
@@ -1413,7 +1413,7 @@
         <v>0.050253976136446</v>
       </c>
       <c r="K24" t="n">
-        <v>8.853799999997137e-06</v>
+        <v>6.86199999472592e-06</v>
       </c>
     </row>
     <row r="25">
@@ -1429,20 +1429,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.26 (2.61)</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.1967392119169235</v>
+        <v>0.256565272808075</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05876800472661853</v>
+        <v>0.05876800417900085</v>
       </c>
       <c r="F25" t="n">
-        <v>0.02821539390087128</v>
+        <v>0.03172695636749268</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0007930694688111544</v>
+        <v>0.0007930694846436381</v>
       </c>
       <c r="H25" t="n">
         <v>0.06216241419315338</v>
@@ -1454,7 +1454,7 @@
         <v>0.04755860194563866</v>
       </c>
       <c r="K25" t="n">
-        <v>7.976599999892641e-06</v>
+        <v>7.428900004015304e-06</v>
       </c>
     </row>
     <row r="26">
@@ -1470,20 +1470,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>10.12 (2.63)</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.2072021725326776</v>
+        <v>0.2292059659957886</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06516785292327404</v>
+        <v>0.06516785174608231</v>
       </c>
       <c r="F26" t="n">
-        <v>0.02550696766376495</v>
+        <v>0.02794837951660156</v>
       </c>
       <c r="G26" t="n">
-        <v>0.000735151925124228</v>
+        <v>0.0007351519307121634</v>
       </c>
       <c r="H26" t="n">
         <v>0.06298694759607315</v>
@@ -1495,7 +1495,7 @@
         <v>0.04773597046732903</v>
       </c>
       <c r="K26" t="n">
-        <v>9.112899999990986e-06</v>
+        <v>6.328499999654014e-06</v>
       </c>
     </row>
     <row r="27">
@@ -1511,20 +1511,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-862.21</t>
+          <t>-862.21 (18.28)</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.0351001445800066</v>
+        <v>0.04733014106750488</v>
       </c>
       <c r="E27" t="n">
-        <v>0.007503213917370886</v>
+        <v>0.007503214292228222</v>
       </c>
       <c r="F27" t="n">
-        <v>8.615534524917603</v>
+        <v>8.668375968933105</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2386340961754322</v>
+        <v>0.2386341094970703</v>
       </c>
       <c r="H27" t="n">
         <v>1.028512477874756</v>
@@ -1536,7 +1536,7 @@
         <v>1.020527601242065</v>
       </c>
       <c r="K27" t="n">
-        <v>5.996800000048097e-06</v>
+        <v>5.165399998077192e-06</v>
       </c>
     </row>
     <row r="28">
@@ -1552,20 +1552,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-279.66</t>
+          <t>-279.66 (4.74)</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.05382232209295034</v>
+        <v>0.0707341730594635</v>
       </c>
       <c r="E28" t="n">
-        <v>0.01563689017668366</v>
+        <v>0.01563688926398754</v>
       </c>
       <c r="F28" t="n">
-        <v>2.926100548267364</v>
+        <v>3.134171009063721</v>
       </c>
       <c r="G28" t="n">
-        <v>0.176208320364356</v>
+        <v>0.1762083172798157</v>
       </c>
       <c r="H28" t="n">
         <v>0.8491321206092834</v>
@@ -1577,7 +1577,7 @@
         <v>1.213654160499573</v>
       </c>
       <c r="K28" t="n">
-        <v>6.301500000063243e-06</v>
+        <v>4.811099999642465e-06</v>
       </c>
     </row>
     <row r="29">
@@ -1593,20 +1593,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-854.43</t>
+          <t>-854.43 (18.09)</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.04216732012853026</v>
+        <v>0.05324763059616089</v>
       </c>
       <c r="E29" t="n">
-        <v>0.008193898860830814</v>
+        <v>0.008193898946046829</v>
       </c>
       <c r="F29" t="n">
-        <v>8.546283812522889</v>
+        <v>8.585378646850586</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2405394058525562</v>
+        <v>0.2405394017696381</v>
       </c>
       <c r="H29" t="n">
         <v>1.011734247207642</v>
@@ -1618,7 +1618,7 @@
         <v>1.073970437049866</v>
       </c>
       <c r="K29" t="n">
-        <v>5.857099999957427e-06</v>
+        <v>5.189300005440601e-06</v>
       </c>
     </row>
     <row r="30">
@@ -1634,20 +1634,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-804.93</t>
+          <t>-804.93 (16.89)</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.03068075277656317</v>
+        <v>0.05677470564842224</v>
       </c>
       <c r="E30" t="n">
-        <v>0.008175390501040965</v>
+        <v>0.008175390772521496</v>
       </c>
       <c r="F30" t="n">
-        <v>8.108450738906861</v>
+        <v>8.155158042907715</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2998057978749275</v>
+        <v>0.2998057901859283</v>
       </c>
       <c r="H30" t="n">
         <v>0.9377399682998657</v>
@@ -1659,7 +1659,7 @@
         <v>1.722495317459106</v>
       </c>
       <c r="K30" t="n">
-        <v>6.437200000164012e-06</v>
+        <v>4.872000004979782e-06</v>
       </c>
     </row>
     <row r="31">
@@ -1675,20 +1675,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-804.90</t>
+          <t>-804.90 (16.92)</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.03261048006638884</v>
+        <v>0.04412353038787842</v>
       </c>
       <c r="E31" t="n">
-        <v>0.006856581707950681</v>
+        <v>0.006856582127511501</v>
       </c>
       <c r="F31" t="n">
-        <v>8.108305682182312</v>
+        <v>8.172106742858887</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3017651666998863</v>
+        <v>0.3017652034759521</v>
       </c>
       <c r="H31" t="n">
         <v>0.9365151524543762</v>
@@ -1700,7 +1700,7 @@
         <v>1.727726340293884</v>
       </c>
       <c r="K31" t="n">
-        <v>6.972700000005716e-06</v>
+        <v>5.273500006296672e-06</v>
       </c>
     </row>
   </sheetData>

--- a/14.xlsx
+++ b/14.xlsx
@@ -486,20 +486,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.76 (3.19)</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.621273040771484</v>
+        <v>1.507521145939827</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1203370690345764</v>
+        <v>0.1203370748758316</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1866598129272461</v>
+        <v>0.1376806048750877</v>
       </c>
       <c r="G2" t="n">
-        <v>0.008726411499083042</v>
+        <v>0.008726411801762878</v>
       </c>
       <c r="H2" t="n">
         <v>1.177233457565308</v>
@@ -511,7 +511,7 @@
         <v>0.06684777140617371</v>
       </c>
       <c r="K2" t="n">
-        <v>1.308379999682074e-05</v>
+        <v>2.96094000004814e-05</v>
       </c>
     </row>
     <row r="3">
@@ -527,20 +527,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.22 (3.20)</t>
+          <t>35.22</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.116897821426392</v>
+        <v>1.095649199485779</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1253170222043991</v>
+        <v>0.1253170286938548</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4395032525062561</v>
+        <v>0.4258854112923146</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03996847569942474</v>
+        <v>0.03996847586706281</v>
       </c>
       <c r="H3" t="n">
         <v>0.1991908848285675</v>
@@ -552,7 +552,7 @@
         <v>0.07220740616321564</v>
       </c>
       <c r="K3" t="n">
-        <v>5.219000006036367e-06</v>
+        <v>5.40020000335062e-06</v>
       </c>
     </row>
     <row r="4">
@@ -568,20 +568,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32.89 (3.15)</t>
+          <t>32.89</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.161139249801636</v>
+        <v>1.118135518312454</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1150936037302017</v>
+        <v>0.1150936045199633</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4398343563079834</v>
+        <v>0.4326098023653031</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04111042991280556</v>
+        <v>0.04111043306067586</v>
       </c>
       <c r="H4" t="n">
         <v>0.195774033665657</v>
@@ -593,7 +593,7 @@
         <v>0.0724397674202919</v>
       </c>
       <c r="K4" t="n">
-        <v>5.549699999392032e-06</v>
+        <v>5.762300002970732e-06</v>
       </c>
     </row>
     <row r="5">
@@ -609,20 +609,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-19.24 (1.93)</t>
+          <t>-19.24</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.722341775894165</v>
+        <v>0.6951915262341499</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1189694404602051</v>
+        <v>0.1189694488272071</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7214891910552979</v>
+        <v>0.7098399860262871</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07070331275463104</v>
+        <v>0.07070331577956676</v>
       </c>
       <c r="H5" t="n">
         <v>0.9304105639457703</v>
@@ -634,7 +634,7 @@
         <v>0.05048612505197525</v>
       </c>
       <c r="K5" t="n">
-        <v>7.174999998824206e-06</v>
+        <v>5.235299999185373e-06</v>
       </c>
     </row>
     <row r="6">
@@ -650,20 +650,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8.17 (2.69)</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1072748750448227</v>
+        <v>0.09126409647613763</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04408286884427071</v>
+        <v>0.04408286951109767</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0746159553527832</v>
+        <v>0.05881992936134339</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001048496924340725</v>
+        <v>0.001048496861942112</v>
       </c>
       <c r="H6" t="n">
         <v>1.187484502792358</v>
@@ -675,7 +675,7 @@
         <v>0.07279366999864578</v>
       </c>
       <c r="K6" t="n">
-        <v>7.185200003732461e-06</v>
+        <v>5.768399998487439e-06</v>
       </c>
     </row>
     <row r="7">
@@ -691,20 +691,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-38.74 (1.45)</t>
+          <t>-38.74</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9931461811065674</v>
+        <v>0.9850751592516899</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1250759959220886</v>
+        <v>0.1250760049149394</v>
       </c>
       <c r="F7" t="n">
-        <v>0.07963383197784424</v>
+        <v>0.07322988539934158</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004229052923619747</v>
+        <v>0.004229053039569408</v>
       </c>
       <c r="H7" t="n">
         <v>0.09441260993480682</v>
@@ -716,7 +716,7 @@
         <v>0.08528155833482742</v>
       </c>
       <c r="K7" t="n">
-        <v>5.321700002241414e-06</v>
+        <v>6.044300003850367e-06</v>
       </c>
     </row>
     <row r="8">
@@ -732,20 +732,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-32.66 (1.61)</t>
+          <t>-32.66</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.05359673500061</v>
+        <v>1.040643057465553</v>
       </c>
       <c r="E8" t="n">
-        <v>0.11422099173069</v>
+        <v>0.1142210026979446</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03472024202346802</v>
+        <v>0.02064226824045181</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001826123479986563</v>
+        <v>0.0001826123488135636</v>
       </c>
       <c r="H8" t="n">
         <v>0.07677828520536423</v>
@@ -757,7 +757,7 @@
         <v>0.09551058709621429</v>
       </c>
       <c r="K8" t="n">
-        <v>6.41939999331953e-06</v>
+        <v>7.693600004131441e-06</v>
       </c>
     </row>
     <row r="9">
@@ -773,20 +773,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-31.81 (1.62)</t>
+          <t>-31.81</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.068664789199829</v>
+        <v>1.050167424440384</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1134010180830956</v>
+        <v>0.1134010265246034</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01989829540252686</v>
+        <v>0.01230723243951798</v>
       </c>
       <c r="G9" t="n">
-        <v>9.615025192033499e-05</v>
+        <v>9.615025343373418e-05</v>
       </c>
       <c r="H9" t="n">
         <v>0.07427655905485153</v>
@@ -798,7 +798,7 @@
         <v>0.09153081476688385</v>
       </c>
       <c r="K9" t="n">
-        <v>5.750200005422812e-06</v>
+        <v>6.180099997436628e-06</v>
       </c>
     </row>
     <row r="10">
@@ -814,20 +814,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-32.96 (1.67)</t>
+          <t>-32.96</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.07895839214325</v>
+        <v>1.036805002570152</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1152711734175682</v>
+        <v>0.1152711741551757</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0432770848274231</v>
+        <v>0.02200803172588348</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0005507275345735252</v>
+        <v>0.0005507275266572833</v>
       </c>
       <c r="H10" t="n">
         <v>1.159277677536011</v>
@@ -839,7 +839,7 @@
         <v>0.09214134514331818</v>
       </c>
       <c r="K10" t="n">
-        <v>6.069899995054584e-06</v>
+        <v>6.042800006980542e-06</v>
       </c>
     </row>
     <row r="11">
@@ -855,20 +855,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-36.82 (1.55)</t>
+          <t>-36.82</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.06371545791626</v>
+        <v>1.03347943687439</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1208392605185509</v>
+        <v>0.120839244261384</v>
       </c>
       <c r="F11" t="n">
-        <v>0.06335258483886719</v>
+        <v>0.05863321894407272</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00205012084916234</v>
+        <v>0.00205012084543705</v>
       </c>
       <c r="H11" t="n">
         <v>0.084022156894207</v>
@@ -880,7 +880,7 @@
         <v>0.1158287227153778</v>
       </c>
       <c r="K11" t="n">
-        <v>6.341000000247732e-06</v>
+        <v>6.669899994449224e-06</v>
       </c>
     </row>
     <row r="12">
@@ -896,20 +896,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-9.68 (2.15)</t>
+          <t>-9.68</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.434185385704041</v>
+        <v>1.416134194135666</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2699629366397858</v>
+        <v>0.2699629244208336</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8818920850753784</v>
+        <v>0.8815997189879418</v>
       </c>
       <c r="G12" t="n">
-        <v>0.09621918946504593</v>
+        <v>0.09621919107437134</v>
       </c>
       <c r="H12" t="n">
         <v>0.6152425408363342</v>
@@ -921,7 +921,7 @@
         <v>0.1135990023612976</v>
       </c>
       <c r="K12" t="n">
-        <v>5.552099995838944e-06</v>
+        <v>5.985000003420282e-06</v>
       </c>
     </row>
     <row r="13">
@@ -937,20 +937,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.40 (3.26)</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9.642556190490723</v>
+        <v>9.318998808860778</v>
       </c>
       <c r="E13" t="n">
-        <v>1.864211440086365</v>
+        <v>1.864211428999901</v>
       </c>
       <c r="F13" t="n">
-        <v>19.41717338562012</v>
+        <v>15.0870366191864</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4467650353908539</v>
+        <v>0.4467650509476662</v>
       </c>
       <c r="H13" t="n">
         <v>0.4047165811061859</v>
@@ -962,7 +962,7 @@
         <v>0.03732327371835709</v>
       </c>
       <c r="K13" t="n">
-        <v>5.686399999831337e-06</v>
+        <v>1.662460000079591e-05</v>
       </c>
     </row>
     <row r="14">
@@ -978,20 +978,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.39 (3.27)</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>9.766969680786133</v>
+        <v>9.402688475608826</v>
       </c>
       <c r="E14" t="n">
-        <v>1.874432563781738</v>
+        <v>1.874432633042336</v>
       </c>
       <c r="F14" t="n">
-        <v>20.11959266662598</v>
+        <v>15.10329270839691</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4530208706855774</v>
+        <v>0.4530208821296692</v>
       </c>
       <c r="H14" t="n">
         <v>0.4066689312458038</v>
@@ -1003,7 +1003,7 @@
         <v>0.03716478496789932</v>
       </c>
       <c r="K14" t="n">
-        <v>5.759599996963516e-06</v>
+        <v>5.929399994784035e-06</v>
       </c>
     </row>
     <row r="15">
@@ -1019,20 +1019,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.39 (3.28)</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>9.508668899536133</v>
+        <v>9.141275308609009</v>
       </c>
       <c r="E15" t="n">
-        <v>1.847036600112915</v>
+        <v>1.84703670156002</v>
       </c>
       <c r="F15" t="n">
-        <v>17.18930244445801</v>
+        <v>14.08442363357544</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5236369371414185</v>
+        <v>0.5236369768381118</v>
       </c>
       <c r="H15" t="n">
         <v>0.3738998472690582</v>
@@ -1044,7 +1044,7 @@
         <v>0.03989281505346298</v>
       </c>
       <c r="K15" t="n">
-        <v>6.512400002975482e-06</v>
+        <v>6.082799998694099e-06</v>
       </c>
     </row>
     <row r="16">
@@ -1060,20 +1060,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.40 (3.27)</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>9.494917869567871</v>
+        <v>9.177847730636596</v>
       </c>
       <c r="E16" t="n">
-        <v>1.861482620239258</v>
+        <v>1.861482509493828</v>
       </c>
       <c r="F16" t="n">
-        <v>17.30372619628906</v>
+        <v>13.84695748519897</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5127214789390564</v>
+        <v>0.5127214749455452</v>
       </c>
       <c r="H16" t="n">
         <v>0.3749077022075653</v>
@@ -1085,7 +1085,7 @@
         <v>0.03747523203492165</v>
       </c>
       <c r="K16" t="n">
-        <v>7.840299993404187e-06</v>
+        <v>6.144800005131401e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1101,14 +1101,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6.02 (3.27)</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.769737720489502</v>
+        <v>1.704965883612633</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1910399496555328</v>
+        <v>0.1910399603992701</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1126,7 +1126,7 @@
         <v>0.05985265970230103</v>
       </c>
       <c r="K17" t="n">
-        <v>7.258700003148988e-06</v>
+        <v>6.509600003482774e-06</v>
       </c>
     </row>
     <row r="18">
@@ -1142,14 +1142,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6.08 (3.25)</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.179211854934692</v>
+        <v>1.13184225165844</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1816953271627426</v>
+        <v>0.1816953220367432</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1167,7 +1167,7 @@
         <v>0.06427808851003647</v>
       </c>
       <c r="K18" t="n">
-        <v>7.395499997073785e-06</v>
+        <v>6.979999998293352e-06</v>
       </c>
     </row>
     <row r="19">
@@ -1183,14 +1183,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6.18 (3.27)</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.229702472686768</v>
+        <v>1.944985589981079</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2022121101617813</v>
+        <v>0.2022121175080538</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1208,7 +1208,7 @@
         <v>0.06141677126288414</v>
       </c>
       <c r="K19" t="n">
-        <v>6.576799998583737e-06</v>
+        <v>6.531399994855747e-06</v>
       </c>
     </row>
     <row r="20">
@@ -1224,14 +1224,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5.97 (3.27)</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.57392954826355</v>
+        <v>1.436445544600487</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1798264980316162</v>
+        <v>0.1798265022188425</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1249,7 +1249,7 @@
         <v>0.05974716320633888</v>
       </c>
       <c r="K20" t="n">
-        <v>7.170400000177324e-06</v>
+        <v>7.487399998353795e-06</v>
       </c>
     </row>
     <row r="21">
@@ -1265,14 +1265,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6.04 (3.26)</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.303850173950195</v>
+        <v>5.079327826976776</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4743886291980743</v>
+        <v>0.4743886026442051</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
         <v>0.06122929230332375</v>
       </c>
       <c r="K21" t="n">
-        <v>6.737799994880334e-06</v>
+        <v>7.544200001575518e-06</v>
       </c>
     </row>
     <row r="22">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9.34 (2.61)</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.2656935453414917</v>
+        <v>0.249610868498683</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06127967685461044</v>
+        <v>0.06127967816591263</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02982461452484131</v>
+        <v>0.02700034844875336</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0006705671548843384</v>
+        <v>0.0006705671008676291</v>
       </c>
       <c r="H22" t="n">
         <v>0.0629999190568924</v>
@@ -1331,7 +1331,7 @@
         <v>0.0472424142062664</v>
       </c>
       <c r="K22" t="n">
-        <v>7.789099996443839e-06</v>
+        <v>7.483999994292389e-06</v>
       </c>
     </row>
     <row r="23">
@@ -1347,20 +1347,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11.68 (2.66)</t>
+          <t>11.68</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.4256680309772491</v>
+        <v>0.3588118672966957</v>
       </c>
       <c r="E23" t="n">
-        <v>0.07536008208990097</v>
+        <v>0.07536008327454329</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0310291051864624</v>
+        <v>0.02798840153217316</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0007254909141920507</v>
+        <v>0.0007254908950999379</v>
       </c>
       <c r="H23" t="n">
         <v>0.06363289803266525</v>
@@ -1372,7 +1372,7 @@
         <v>0.04826546832919121</v>
       </c>
       <c r="K23" t="n">
-        <v>6.846100004622712e-06</v>
+        <v>7.949499995447695e-06</v>
       </c>
     </row>
     <row r="24">
@@ -1388,20 +1388,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.25 (2.52)</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.3833224773406982</v>
+        <v>0.3503062247335911</v>
       </c>
       <c r="E24" t="n">
-        <v>0.07651928812265396</v>
+        <v>0.07651928365975619</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02307343482971191</v>
+        <v>0.02270333027839661</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0002378217614023015</v>
+        <v>0.0002378217522054911</v>
       </c>
       <c r="H24" t="n">
         <v>0.06166854873299599</v>
@@ -1413,7 +1413,7 @@
         <v>0.050253976136446</v>
       </c>
       <c r="K24" t="n">
-        <v>6.86199999472592e-06</v>
+        <v>7.066999998642132e-06</v>
       </c>
     </row>
     <row r="25">
@@ -1429,20 +1429,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>9.26 (2.61)</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.256565272808075</v>
+        <v>0.1967392119169235</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05876800417900085</v>
+        <v>0.05876800472661853</v>
       </c>
       <c r="F25" t="n">
-        <v>0.03172695636749268</v>
+        <v>0.02821539390087128</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0007930694846436381</v>
+        <v>0.0007930694688111544</v>
       </c>
       <c r="H25" t="n">
         <v>0.06216241419315338</v>
@@ -1454,7 +1454,7 @@
         <v>0.04755860194563866</v>
       </c>
       <c r="K25" t="n">
-        <v>7.428900004015304e-06</v>
+        <v>7.523599997512065e-06</v>
       </c>
     </row>
     <row r="26">
@@ -1470,20 +1470,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>10.12 (2.63)</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.2292059659957886</v>
+        <v>0.2072021725326776</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06516785174608231</v>
+        <v>0.06516785292327404</v>
       </c>
       <c r="F26" t="n">
-        <v>0.02794837951660156</v>
+        <v>0.02550696766376495</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0007351519307121634</v>
+        <v>0.000735151925124228</v>
       </c>
       <c r="H26" t="n">
         <v>0.06298694759607315</v>
@@ -1495,7 +1495,7 @@
         <v>0.04773597046732903</v>
       </c>
       <c r="K26" t="n">
-        <v>6.328499999654014e-06</v>
+        <v>8.149499997671227e-06</v>
       </c>
     </row>
     <row r="27">
@@ -1511,20 +1511,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-862.21 (18.28)</t>
+          <t>-862.21</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.04733014106750488</v>
+        <v>0.0351001445800066</v>
       </c>
       <c r="E27" t="n">
-        <v>0.007503214292228222</v>
+        <v>0.007503213917370886</v>
       </c>
       <c r="F27" t="n">
-        <v>8.668375968933105</v>
+        <v>8.615534524917603</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2386341094970703</v>
+        <v>0.2386340961754322</v>
       </c>
       <c r="H27" t="n">
         <v>1.028512477874756</v>
@@ -1536,7 +1536,7 @@
         <v>1.020527601242065</v>
       </c>
       <c r="K27" t="n">
-        <v>5.165399998077192e-06</v>
+        <v>5.456799997773488e-06</v>
       </c>
     </row>
     <row r="28">
@@ -1552,20 +1552,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-279.66 (4.74)</t>
+          <t>-279.66</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.0707341730594635</v>
+        <v>0.05382232209295034</v>
       </c>
       <c r="E28" t="n">
-        <v>0.01563688926398754</v>
+        <v>0.01563689017668366</v>
       </c>
       <c r="F28" t="n">
-        <v>3.134171009063721</v>
+        <v>2.926100548267364</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1762083172798157</v>
+        <v>0.176208320364356</v>
       </c>
       <c r="H28" t="n">
         <v>0.8491321206092834</v>
@@ -1577,7 +1577,7 @@
         <v>1.213654160499573</v>
       </c>
       <c r="K28" t="n">
-        <v>4.811099999642465e-06</v>
+        <v>6.082299994886853e-06</v>
       </c>
     </row>
     <row r="29">
@@ -1593,20 +1593,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-854.43 (18.09)</t>
+          <t>-854.43</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.05324763059616089</v>
+        <v>0.04216732012853026</v>
       </c>
       <c r="E29" t="n">
-        <v>0.008193898946046829</v>
+        <v>0.008193898860830814</v>
       </c>
       <c r="F29" t="n">
-        <v>8.585378646850586</v>
+        <v>8.546283812522889</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2405394017696381</v>
+        <v>0.2405394058525562</v>
       </c>
       <c r="H29" t="n">
         <v>1.011734247207642</v>
@@ -1618,7 +1618,7 @@
         <v>1.073970437049866</v>
       </c>
       <c r="K29" t="n">
-        <v>5.189300005440601e-06</v>
+        <v>5.453199999465142e-06</v>
       </c>
     </row>
     <row r="30">
@@ -1634,20 +1634,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-804.93 (16.89)</t>
+          <t>-804.93</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.05677470564842224</v>
+        <v>0.03068075277656317</v>
       </c>
       <c r="E30" t="n">
-        <v>0.008175390772521496</v>
+        <v>0.008175390501040965</v>
       </c>
       <c r="F30" t="n">
-        <v>8.155158042907715</v>
+        <v>8.108450738906861</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2998057901859283</v>
+        <v>0.2998057978749275</v>
       </c>
       <c r="H30" t="n">
         <v>0.9377399682998657</v>
@@ -1659,7 +1659,7 @@
         <v>1.722495317459106</v>
       </c>
       <c r="K30" t="n">
-        <v>4.872000004979782e-06</v>
+        <v>5.466599999635946e-06</v>
       </c>
     </row>
     <row r="31">
@@ -1675,20 +1675,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-804.90 (16.92)</t>
+          <t>-804.90</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.04412353038787842</v>
+        <v>0.03261048006638884</v>
       </c>
       <c r="E31" t="n">
-        <v>0.006856582127511501</v>
+        <v>0.006856581707950681</v>
       </c>
       <c r="F31" t="n">
-        <v>8.172106742858887</v>
+        <v>8.108305682182312</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3017652034759521</v>
+        <v>0.3017651666998863</v>
       </c>
       <c r="H31" t="n">
         <v>0.9365151524543762</v>
@@ -1700,7 +1700,7 @@
         <v>1.727726340293884</v>
       </c>
       <c r="K31" t="n">
-        <v>5.273500006296672e-06</v>
+        <v>5.760499996540602e-06</v>
       </c>
     </row>
   </sheetData>

--- a/14.xlsx
+++ b/14.xlsx
@@ -511,7 +511,7 @@
         <v>0.06684777140617371</v>
       </c>
       <c r="K2" t="n">
-        <v>2.96094000004814e-05</v>
+        <v>1.212620000296738e-05</v>
       </c>
     </row>
     <row r="3">
@@ -552,7 +552,7 @@
         <v>0.07220740616321564</v>
       </c>
       <c r="K3" t="n">
-        <v>5.40020000335062e-06</v>
+        <v>5.606699996860698e-06</v>
       </c>
     </row>
     <row r="4">
@@ -593,7 +593,7 @@
         <v>0.0724397674202919</v>
       </c>
       <c r="K4" t="n">
-        <v>5.762300002970732e-06</v>
+        <v>5.725900002289564e-06</v>
       </c>
     </row>
     <row r="5">
@@ -634,7 +634,7 @@
         <v>0.05048612505197525</v>
       </c>
       <c r="K5" t="n">
-        <v>5.235299999185373e-06</v>
+        <v>5.719699998735451e-06</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +675,7 @@
         <v>0.07279366999864578</v>
       </c>
       <c r="K6" t="n">
-        <v>5.768399998487439e-06</v>
+        <v>6.898500003444497e-06</v>
       </c>
     </row>
     <row r="7">
@@ -716,7 +716,7 @@
         <v>0.08528155833482742</v>
       </c>
       <c r="K7" t="n">
-        <v>6.044300003850367e-06</v>
+        <v>6.226400000741705e-06</v>
       </c>
     </row>
     <row r="8">
@@ -757,7 +757,7 @@
         <v>0.09551058709621429</v>
       </c>
       <c r="K8" t="n">
-        <v>7.693600004131441e-06</v>
+        <v>7.095300003129523e-06</v>
       </c>
     </row>
     <row r="9">
@@ -798,7 +798,7 @@
         <v>0.09153081476688385</v>
       </c>
       <c r="K9" t="n">
-        <v>6.180099997436628e-06</v>
+        <v>6.261900001845788e-06</v>
       </c>
     </row>
     <row r="10">
@@ -839,7 +839,7 @@
         <v>0.09214134514331818</v>
       </c>
       <c r="K10" t="n">
-        <v>6.042800006980542e-06</v>
+        <v>8.014300001377705e-06</v>
       </c>
     </row>
     <row r="11">
@@ -880,7 +880,7 @@
         <v>0.1158287227153778</v>
       </c>
       <c r="K11" t="n">
-        <v>6.669899994449224e-06</v>
+        <v>6.371399998897686e-06</v>
       </c>
     </row>
     <row r="12">
@@ -921,7 +921,7 @@
         <v>0.1135990023612976</v>
       </c>
       <c r="K12" t="n">
-        <v>5.985000003420282e-06</v>
+        <v>6.276200001593679e-06</v>
       </c>
     </row>
     <row r="13">
@@ -962,7 +962,7 @@
         <v>0.03732327371835709</v>
       </c>
       <c r="K13" t="n">
-        <v>1.662460000079591e-05</v>
+        <v>5.923800003074575e-06</v>
       </c>
     </row>
     <row r="14">
@@ -1003,7 +1003,7 @@
         <v>0.03716478496789932</v>
       </c>
       <c r="K14" t="n">
-        <v>5.929399994784035e-06</v>
+        <v>6.431899993913249e-06</v>
       </c>
     </row>
     <row r="15">
@@ -1044,7 +1044,7 @@
         <v>0.03989281505346298</v>
       </c>
       <c r="K15" t="n">
-        <v>6.082799998694099e-06</v>
+        <v>7.291200003237464e-06</v>
       </c>
     </row>
     <row r="16">
@@ -1085,7 +1085,7 @@
         <v>0.03747523203492165</v>
       </c>
       <c r="K16" t="n">
-        <v>6.144800005131401e-06</v>
+        <v>9.979099995689467e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1126,7 +1126,7 @@
         <v>0.05985265970230103</v>
       </c>
       <c r="K17" t="n">
-        <v>6.509600003482774e-06</v>
+        <v>1.136630000110017e-05</v>
       </c>
     </row>
     <row r="18">
@@ -1167,7 +1167,7 @@
         <v>0.06427808851003647</v>
       </c>
       <c r="K18" t="n">
-        <v>6.979999998293352e-06</v>
+        <v>1.090789999580011e-05</v>
       </c>
     </row>
     <row r="19">
@@ -1208,7 +1208,7 @@
         <v>0.06141677126288414</v>
       </c>
       <c r="K19" t="n">
-        <v>6.531399994855747e-06</v>
+        <v>7.796600002620834e-06</v>
       </c>
     </row>
     <row r="20">
@@ -1249,7 +1249,7 @@
         <v>0.05974716320633888</v>
       </c>
       <c r="K20" t="n">
-        <v>7.487399998353795e-06</v>
+        <v>1.256879999709781e-05</v>
       </c>
     </row>
     <row r="21">
@@ -1290,7 +1290,7 @@
         <v>0.06122929230332375</v>
       </c>
       <c r="K21" t="n">
-        <v>7.544200001575518e-06</v>
+        <v>1.275150000583381e-05</v>
       </c>
     </row>
     <row r="22">
@@ -1331,7 +1331,7 @@
         <v>0.0472424142062664</v>
       </c>
       <c r="K22" t="n">
-        <v>7.483999994292389e-06</v>
+        <v>1.424050000059651e-05</v>
       </c>
     </row>
     <row r="23">
@@ -1372,7 +1372,7 @@
         <v>0.04826546832919121</v>
       </c>
       <c r="K23" t="n">
-        <v>7.949499995447695e-06</v>
+        <v>4.547939999611117e-05</v>
       </c>
     </row>
     <row r="24">
@@ -1413,7 +1413,7 @@
         <v>0.050253976136446</v>
       </c>
       <c r="K24" t="n">
-        <v>7.066999998642132e-06</v>
+        <v>1.738040000054753e-05</v>
       </c>
     </row>
     <row r="25">
@@ -1454,7 +1454,7 @@
         <v>0.04755860194563866</v>
       </c>
       <c r="K25" t="n">
-        <v>7.523599997512065e-06</v>
+        <v>1.528030000190483e-05</v>
       </c>
     </row>
     <row r="26">
@@ -1495,7 +1495,7 @@
         <v>0.04773597046732903</v>
       </c>
       <c r="K26" t="n">
-        <v>8.149499997671227e-06</v>
+        <v>1.414710000244668e-05</v>
       </c>
     </row>
     <row r="27">
@@ -1536,7 +1536,7 @@
         <v>1.020527601242065</v>
       </c>
       <c r="K27" t="n">
-        <v>5.456799997773488e-06</v>
+        <v>3.877290000673383e-05</v>
       </c>
     </row>
     <row r="28">
@@ -1577,7 +1577,7 @@
         <v>1.213654160499573</v>
       </c>
       <c r="K28" t="n">
-        <v>6.082299994886853e-06</v>
+        <v>1.20463000057498e-05</v>
       </c>
     </row>
     <row r="29">
@@ -1618,7 +1618,7 @@
         <v>1.073970437049866</v>
       </c>
       <c r="K29" t="n">
-        <v>5.453199999465142e-06</v>
+        <v>1.078060000145342e-05</v>
       </c>
     </row>
     <row r="30">
@@ -1659,7 +1659,7 @@
         <v>1.722495317459106</v>
       </c>
       <c r="K30" t="n">
-        <v>5.466599999635946e-06</v>
+        <v>6.258599998545833e-06</v>
       </c>
     </row>
     <row r="31">
@@ -1700,7 +1700,7 @@
         <v>1.727726340293884</v>
       </c>
       <c r="K31" t="n">
-        <v>5.760499996540602e-06</v>
+        <v>6.226099998457357e-06</v>
       </c>
     </row>
   </sheetData>
